--- a/outputs/FQY1530_FC1402_稼働調整速度.xlsx
+++ b/outputs/FQY1530_FC1402_稼働調整速度.xlsx
@@ -11,6 +11,7 @@
     <sheet name="S_U一覧" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="調整イベント一覧" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="代表S_Uトレンド" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="計画と実績_重ね書き" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,10 +20,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd hh:mm"/>
+    <numFmt numFmtId="165" formatCode="yyyy/mm/dd hh:mm"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -56,12 +56,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -588,6 +589,380 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>増量開始からの FC1402 増分 [T/H]</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'計画と実績_重ね書き'!B11</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'計画と実績_重ね書き'!$A$12:$A$22</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'計画と実績_重ね書き'!$B$12:$B$22</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'計画と実績_重ね書き'!C11</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'計画と実績_重ね書き'!$A$12:$A$22</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'計画と実績_重ね書き'!$C$12:$C$22</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'計画と実績_重ね書き'!D11</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'計画と実績_重ね書き'!$A$12:$A$22</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'計画と実績_重ね書き'!$D$12:$D$22</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'計画と実績_重ね書き'!E11</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'計画と実績_重ね書き'!$A$12:$A$22</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'計画と実績_重ね書き'!$E$12:$E$22</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'計画と実績_重ね書き'!F11</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'計画と実績_重ね書き'!$A$12:$A$22</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'計画と実績_重ね書き'!$F$12:$F$22</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <tx>
+            <strRef>
+              <f>'計画と実績_重ね書き'!G11</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'計画と実績_重ね書き'!$A$12:$A$22</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'計画と実績_重ね書き'!$G$12:$G$22</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="6"/>
+          <order val="6"/>
+          <tx>
+            <strRef>
+              <f>'計画と実績_重ね書き'!H11</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'計画と実績_重ね書き'!$A$12:$A$22</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'計画と実績_重ね書き'!$H$12:$H$22</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="7"/>
+          <order val="7"/>
+          <tx>
+            <strRef>
+              <f>'計画と実績_重ね書き'!I11</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'計画と実績_重ね書き'!$A$12:$A$22</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'計画と実績_重ね書き'!$I$12:$I$22</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="8"/>
+          <order val="8"/>
+          <tx>
+            <strRef>
+              <f>'計画と実績_重ね書き'!J11</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'計画と実績_重ね書き'!$A$12:$A$22</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'計画と実績_重ね書き'!$J$12:$J$22</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>経過時間 [h]</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>FC1402 の増分 [T/H]</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -651,6 +1026,33 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>12</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1709,16 +2111,16 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>43958.16666666666</v>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="5" t="n">
         <v>43966.375</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>197</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="5" t="n">
         <v>43958.91666666666</v>
       </c>
       <c r="E4" s="2" t="n">
@@ -1751,19 +2153,18 @@
       <c r="N4" s="2" t="n">
         <v>18.01368268330892</v>
       </c>
-      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>43967.91666666666</v>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="5" t="n">
         <v>43972.83333333334</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>118</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="5" t="n">
         <v>43968.91666666666</v>
       </c>
       <c r="E5" s="2" t="n">
@@ -1796,19 +2197,18 @@
       <c r="N5" s="2" t="n">
         <v>17.96332113204464</v>
       </c>
-      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>44007.45833333334</v>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="5" t="n">
         <v>44353.375</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>8302</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="5" t="n">
         <v>44007.375</v>
       </c>
       <c r="E6" s="2" t="n">
@@ -1825,13 +2225,12 @@
       <c r="N6" s="2" t="n">
         <v>20.70647795889113</v>
       </c>
-      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>44354.54166666666</v>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B7" s="5" t="n">
         <v>44367.04166666666</v>
       </c>
       <c r="C7" s="2" t="n">
@@ -1856,10 +2255,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>44367.20833333334</v>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="5" t="n">
         <v>44372.33333333334</v>
       </c>
       <c r="C8" s="2" t="n">
@@ -1884,16 +2283,16 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>44376.54166666666</v>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B9" s="5" t="n">
         <v>44412.5</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>863</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" s="5" t="n">
         <v>44377.33333333334</v>
       </c>
       <c r="E9" s="2" t="n">
@@ -1926,19 +2325,18 @@
       <c r="N9" s="2" t="n">
         <v>19.06180877155728</v>
       </c>
-      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>44414.25</v>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" s="5" t="n">
         <v>44429.33333333334</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>362</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" s="5" t="n">
         <v>44415</v>
       </c>
       <c r="E10" s="2" t="n">
@@ -1971,19 +2369,18 @@
       <c r="N10" s="2" t="n">
         <v>17.65555196020338</v>
       </c>
-      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>44429.91666666666</v>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="5" t="n">
         <v>44622.41666666666</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>4620</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" s="5" t="n">
         <v>44430.625</v>
       </c>
       <c r="E11" s="2" t="n">
@@ -2016,19 +2413,18 @@
       <c r="N11" s="2" t="n">
         <v>19.61427842564053</v>
       </c>
-      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>44625.41666666666</v>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" s="5" t="n">
         <v>44696.125</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>1697</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" s="5" t="n">
         <v>44626.125</v>
       </c>
       <c r="E12" s="2" t="n">
@@ -2061,13 +2457,12 @@
       <c r="N12" s="2" t="n">
         <v>18.18273360888164</v>
       </c>
-      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>44697.79166666666</v>
       </c>
-      <c r="B13" s="3" t="n">
+      <c r="B13" s="5" t="n">
         <v>44708.58333333334</v>
       </c>
       <c r="C13" s="2" t="n">
@@ -2092,16 +2487,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>44714.375</v>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B14" s="5" t="n">
         <v>44935.45833333334</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>5306</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D14" s="5" t="n">
         <v>44736.45833333334</v>
       </c>
       <c r="E14" s="2" t="n">
@@ -2141,16 +2536,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>44962.33333333334</v>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B15" s="5" t="n">
         <v>45054.83333333334</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>2220</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="D15" s="5" t="n">
         <v>44963.5</v>
       </c>
       <c r="E15" s="2" t="n">
@@ -2183,19 +2578,18 @@
       <c r="N15" s="2" t="n">
         <v>17.00464226033953</v>
       </c>
-      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>45066.625</v>
       </c>
-      <c r="B16" s="3" t="n">
+      <c r="B16" s="5" t="n">
         <v>45097.45833333334</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>740</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D16" s="5" t="n">
         <v>45067.375</v>
       </c>
       <c r="E16" s="2" t="n">
@@ -2228,19 +2622,18 @@
       <c r="N16" s="2" t="n">
         <v>15.33010002639559</v>
       </c>
-      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>45098.875</v>
       </c>
-      <c r="B17" s="3" t="n">
+      <c r="B17" s="5" t="n">
         <v>45103.83333333334</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>119</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="D17" s="5" t="n">
         <v>45100.16666666666</v>
       </c>
       <c r="E17" s="2" t="n">
@@ -2273,13 +2666,12 @@
       <c r="N17" s="2" t="n">
         <v>10.32982587655385</v>
       </c>
-      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>45128.58333333334</v>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B18" s="5" t="n">
         <v>45139.75</v>
       </c>
       <c r="C18" s="2" t="n">
@@ -2304,16 +2696,16 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>45147.29166666666</v>
       </c>
-      <c r="B19" s="3" t="n">
+      <c r="B19" s="5" t="n">
         <v>45170.41666666666</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>555</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="D19" s="5" t="n">
         <v>45148.41666666666</v>
       </c>
       <c r="E19" s="2" t="n">
@@ -2346,13 +2738,12 @@
       <c r="N19" s="2" t="n">
         <v>14.80079474343194</v>
       </c>
-      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>45171.08333333334</v>
       </c>
-      <c r="B20" s="3" t="n">
+      <c r="B20" s="5" t="n">
         <v>45179.29166666666</v>
       </c>
       <c r="C20" s="2" t="n">
@@ -2377,16 +2768,16 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>45179.41666666666</v>
       </c>
-      <c r="B21" s="3" t="n">
+      <c r="B21" s="5" t="n">
         <v>45193.95833333334</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>349</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="D21" s="5" t="n">
         <v>45180.41666666666</v>
       </c>
       <c r="E21" s="2" t="n">
@@ -2419,19 +2810,18 @@
       <c r="N21" s="2" t="n">
         <v>15.00911128150092</v>
       </c>
-      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>45195.54166666666</v>
       </c>
-      <c r="B22" s="3" t="n">
+      <c r="B22" s="5" t="n">
         <v>45251.79166666666</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>1350</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="D22" s="5" t="n">
         <v>45196.25</v>
       </c>
       <c r="E22" s="2" t="n">
@@ -2464,13 +2854,12 @@
       <c r="N22" s="2" t="n">
         <v>13.99961425251431</v>
       </c>
-      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>45254.25</v>
       </c>
-      <c r="B23" s="3" t="n">
+      <c r="B23" s="5" t="n">
         <v>45256.875</v>
       </c>
       <c r="C23" s="2" t="n">
@@ -2495,16 +2884,16 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>45257.79166666666</v>
       </c>
-      <c r="B24" s="3" t="n">
+      <c r="B24" s="5" t="n">
         <v>45419.33333333334</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>3877</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="D24" s="5" t="n">
         <v>45258.33333333334</v>
       </c>
       <c r="E24" s="2" t="n">
@@ -2537,19 +2926,18 @@
       <c r="N24" s="2" t="n">
         <v>15.00844380696614</v>
       </c>
-      <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>45463.66666666666</v>
       </c>
-      <c r="B25" s="3" t="n">
+      <c r="B25" s="5" t="n">
         <v>45468.91666666666</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>126</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="D25" s="5" t="n">
         <v>45464.91666666666</v>
       </c>
       <c r="E25" s="2" t="n">
@@ -2582,19 +2970,18 @@
       <c r="N25" s="2" t="n">
         <v>12.02423935890198</v>
       </c>
-      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>45469.79166666666</v>
       </c>
-      <c r="B26" s="3" t="n">
+      <c r="B26" s="5" t="n">
         <v>45666.29166666666</v>
       </c>
       <c r="C26" s="2" t="n">
         <v>4716</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="D26" s="5" t="n">
         <v>45470.29166666666</v>
       </c>
       <c r="E26" s="2" t="n">
@@ -2627,13 +3014,12 @@
       <c r="N26" s="2" t="n">
         <v>19.07297427919176</v>
       </c>
-      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>45668.75</v>
       </c>
-      <c r="B27" s="3" t="n">
+      <c r="B27" s="5" t="n">
         <v>45674.375</v>
       </c>
       <c r="C27" s="2" t="n">
@@ -2658,16 +3044,16 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>45705</v>
       </c>
-      <c r="B28" s="3" t="n">
+      <c r="B28" s="5" t="n">
         <v>45811.54166666666</v>
       </c>
       <c r="C28" s="2" t="n">
         <v>2557</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="D28" s="5" t="n">
         <v>45706.75</v>
       </c>
       <c r="E28" s="2" t="n">
@@ -2700,19 +3086,18 @@
       <c r="N28" s="2" t="n">
         <v>19.20332738134596</v>
       </c>
-      <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>45860.45833333334</v>
       </c>
-      <c r="B29" s="3" t="n">
+      <c r="B29" s="5" t="n">
         <v>46011.45833333334</v>
       </c>
       <c r="C29" s="2" t="n">
         <v>3624</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="D29" s="5" t="n">
         <v>45862</v>
       </c>
       <c r="E29" s="2" t="n">
@@ -2745,13 +3130,12 @@
       <c r="N29" s="2" t="n">
         <v>18.20981524573432</v>
       </c>
-      <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>46067.875</v>
       </c>
-      <c r="B30" s="3" t="n">
+      <c r="B30" s="5" t="n">
         <v>46070.04166666666</v>
       </c>
       <c r="C30" s="2" t="n">
@@ -2776,16 +3160,16 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>46078.375</v>
       </c>
-      <c r="B31" s="3" t="n">
+      <c r="B31" s="5" t="n">
         <v>46152.95833333334</v>
       </c>
       <c r="C31" s="2" t="n">
         <v>1790</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="D31" s="5" t="n">
         <v>46079.54166666666</v>
       </c>
       <c r="E31" s="2" t="n">
@@ -2818,7 +3202,6 @@
       <c r="N31" s="2" t="n">
         <v>11.3211573823293</v>
       </c>
-      <c r="O31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2930,10 +3313,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>43834.625</v>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="5" t="n">
         <v>43834.79166666666</v>
       </c>
       <c r="C4" s="2" t="n">
@@ -2980,10 +3363,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>43839.16666666666</v>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="5" t="n">
         <v>43839.66666666666</v>
       </c>
       <c r="C5" s="2" t="n">
@@ -3030,10 +3413,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>43844.625</v>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="5" t="n">
         <v>43844.95833333334</v>
       </c>
       <c r="C6" s="2" t="n">
@@ -3080,10 +3463,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>43845.66666666666</v>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B7" s="5" t="n">
         <v>43846.20833333334</v>
       </c>
       <c r="C7" s="2" t="n">
@@ -3130,10 +3513,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>43846.79166666666</v>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="5" t="n">
         <v>43847</v>
       </c>
       <c r="C8" s="2" t="n">
@@ -3180,10 +3563,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>43853.16666666666</v>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B9" s="5" t="n">
         <v>43853.41666666666</v>
       </c>
       <c r="C9" s="2" t="n">
@@ -3230,10 +3613,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>43857.66666666666</v>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" s="5" t="n">
         <v>43858.5</v>
       </c>
       <c r="C10" s="2" t="n">
@@ -3280,10 +3663,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>43858.625</v>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="5" t="n">
         <v>43859.08333333334</v>
       </c>
       <c r="C11" s="2" t="n">
@@ -3330,10 +3713,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>43859.70833333334</v>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" s="5" t="n">
         <v>43860</v>
       </c>
       <c r="C12" s="2" t="n">
@@ -3380,10 +3763,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>43860.5</v>
       </c>
-      <c r="B13" s="3" t="n">
+      <c r="B13" s="5" t="n">
         <v>43861.41666666666</v>
       </c>
       <c r="C13" s="2" t="n">
@@ -3430,10 +3813,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>43862.16666666666</v>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B14" s="5" t="n">
         <v>43862.54166666666</v>
       </c>
       <c r="C14" s="2" t="n">
@@ -3480,10 +3863,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>43887.16666666666</v>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B15" s="5" t="n">
         <v>43887.375</v>
       </c>
       <c r="C15" s="2" t="n">
@@ -3530,10 +3913,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>43888.29166666666</v>
       </c>
-      <c r="B16" s="3" t="n">
+      <c r="B16" s="5" t="n">
         <v>43888.625</v>
       </c>
       <c r="C16" s="2" t="n">
@@ -3580,10 +3963,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>43892.45833333334</v>
       </c>
-      <c r="B17" s="3" t="n">
+      <c r="B17" s="5" t="n">
         <v>43892.95833333334</v>
       </c>
       <c r="C17" s="2" t="n">
@@ -3630,10 +4013,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>43896.41666666666</v>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B18" s="5" t="n">
         <v>43896.95833333334</v>
       </c>
       <c r="C18" s="2" t="n">
@@ -3680,10 +4063,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>43899.29166666666</v>
       </c>
-      <c r="B19" s="3" t="n">
+      <c r="B19" s="5" t="n">
         <v>43899.83333333334</v>
       </c>
       <c r="C19" s="2" t="n">
@@ -3730,10 +4113,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>43914.58333333334</v>
       </c>
-      <c r="B20" s="3" t="n">
+      <c r="B20" s="5" t="n">
         <v>43914.95833333334</v>
       </c>
       <c r="C20" s="2" t="n">
@@ -3780,10 +4163,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>43916.625</v>
       </c>
-      <c r="B21" s="3" t="n">
+      <c r="B21" s="5" t="n">
         <v>43917.08333333334</v>
       </c>
       <c r="C21" s="2" t="n">
@@ -3830,10 +4213,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>43920.45833333334</v>
       </c>
-      <c r="B22" s="3" t="n">
+      <c r="B22" s="5" t="n">
         <v>43921.25</v>
       </c>
       <c r="C22" s="2" t="n">
@@ -3880,10 +4263,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>43921.41666666666</v>
       </c>
-      <c r="B23" s="3" t="n">
+      <c r="B23" s="5" t="n">
         <v>43922.66666666666</v>
       </c>
       <c r="C23" s="2" t="n">
@@ -3930,10 +4313,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>43922.83333333334</v>
       </c>
-      <c r="B24" s="3" t="n">
+      <c r="B24" s="5" t="n">
         <v>43923.20833333334</v>
       </c>
       <c r="C24" s="2" t="n">
@@ -3980,10 +4363,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>43923.54166666666</v>
       </c>
-      <c r="B25" s="3" t="n">
+      <c r="B25" s="5" t="n">
         <v>43924.875</v>
       </c>
       <c r="C25" s="2" t="n">
@@ -4030,10 +4413,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>43930.95833333334</v>
       </c>
-      <c r="B26" s="3" t="n">
+      <c r="B26" s="5" t="n">
         <v>43931.125</v>
       </c>
       <c r="C26" s="2" t="n">
@@ -4080,10 +4463,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>43931.75</v>
       </c>
-      <c r="B27" s="3" t="n">
+      <c r="B27" s="5" t="n">
         <v>43932.66666666666</v>
       </c>
       <c r="C27" s="2" t="n">
@@ -4130,10 +4513,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>43936.20833333334</v>
       </c>
-      <c r="B28" s="3" t="n">
+      <c r="B28" s="5" t="n">
         <v>43937.20833333334</v>
       </c>
       <c r="C28" s="2" t="n">
@@ -4180,10 +4563,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>43937.58333333334</v>
       </c>
-      <c r="B29" s="3" t="n">
+      <c r="B29" s="5" t="n">
         <v>43938.04166666666</v>
       </c>
       <c r="C29" s="2" t="n">
@@ -4230,10 +4613,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>43952</v>
       </c>
-      <c r="B30" s="3" t="n">
+      <c r="B30" s="5" t="n">
         <v>43952.33333333334</v>
       </c>
       <c r="C30" s="2" t="n">
@@ -4280,10 +4663,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>43956.91666666666</v>
       </c>
-      <c r="B31" s="3" t="n">
+      <c r="B31" s="5" t="n">
         <v>43957.16666666666</v>
       </c>
       <c r="C31" s="2" t="n">
@@ -4330,10 +4713,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>43958.125</v>
       </c>
-      <c r="B32" s="3" t="n">
+      <c r="B32" s="5" t="n">
         <v>43959.29166666666</v>
       </c>
       <c r="C32" s="2" t="n">
@@ -4380,10 +4763,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>43959.75</v>
       </c>
-      <c r="B33" s="3" t="n">
+      <c r="B33" s="5" t="n">
         <v>43959.95833333334</v>
       </c>
       <c r="C33" s="2" t="n">
@@ -4430,10 +4813,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>43960.125</v>
       </c>
-      <c r="B34" s="3" t="n">
+      <c r="B34" s="5" t="n">
         <v>43960.91666666666</v>
       </c>
       <c r="C34" s="2" t="n">
@@ -4480,10 +4863,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>43962.79166666666</v>
       </c>
-      <c r="B35" s="3" t="n">
+      <c r="B35" s="5" t="n">
         <v>43963.04166666666</v>
       </c>
       <c r="C35" s="2" t="n">
@@ -4530,10 +4913,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>43965.83333333334</v>
       </c>
-      <c r="B36" s="3" t="n">
+      <c r="B36" s="5" t="n">
         <v>43966.41666666666</v>
       </c>
       <c r="C36" s="2" t="n">
@@ -4580,10 +4963,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>43967.875</v>
       </c>
-      <c r="B37" s="3" t="n">
+      <c r="B37" s="5" t="n">
         <v>43968.33333333334</v>
       </c>
       <c r="C37" s="2" t="n">
@@ -4630,10 +5013,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>43968.45833333334</v>
       </c>
-      <c r="B38" s="3" t="n">
+      <c r="B38" s="5" t="n">
         <v>43970.95833333334</v>
       </c>
       <c r="C38" s="2" t="n">
@@ -4680,10 +5063,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>43972.41666666666</v>
       </c>
-      <c r="B39" s="3" t="n">
+      <c r="B39" s="5" t="n">
         <v>43972.79166666666</v>
       </c>
       <c r="C39" s="2" t="n">
@@ -4730,10 +5113,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>44007.41666666666</v>
       </c>
-      <c r="B40" s="3" t="n">
+      <c r="B40" s="5" t="n">
         <v>44007.83333333334</v>
       </c>
       <c r="C40" s="2" t="n">
@@ -4780,10 +5163,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>44008.29166666666</v>
       </c>
-      <c r="B41" s="3" t="n">
+      <c r="B41" s="5" t="n">
         <v>44008.45833333334</v>
       </c>
       <c r="C41" s="2" t="n">
@@ -4830,10 +5213,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="5" t="n">
         <v>44008.79166666666</v>
       </c>
-      <c r="B42" s="3" t="n">
+      <c r="B42" s="5" t="n">
         <v>44009.375</v>
       </c>
       <c r="C42" s="2" t="n">
@@ -4880,10 +5263,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="5" t="n">
         <v>44009.54166666666</v>
       </c>
-      <c r="B43" s="3" t="n">
+      <c r="B43" s="5" t="n">
         <v>44009.70833333334</v>
       </c>
       <c r="C43" s="2" t="n">
@@ -4930,10 +5313,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="5" t="n">
         <v>44009.83333333334</v>
       </c>
-      <c r="B44" s="3" t="n">
+      <c r="B44" s="5" t="n">
         <v>44010.20833333334</v>
       </c>
       <c r="C44" s="2" t="n">
@@ -4980,10 +5363,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="5" t="n">
         <v>44013.5</v>
       </c>
-      <c r="B45" s="3" t="n">
+      <c r="B45" s="5" t="n">
         <v>44013.79166666666</v>
       </c>
       <c r="C45" s="2" t="n">
@@ -5030,10 +5413,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="5" t="n">
         <v>44014.66666666666</v>
       </c>
-      <c r="B46" s="3" t="n">
+      <c r="B46" s="5" t="n">
         <v>44014.83333333334</v>
       </c>
       <c r="C46" s="2" t="n">
@@ -5080,10 +5463,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="5" t="n">
         <v>44021.04166666666</v>
       </c>
-      <c r="B47" s="3" t="n">
+      <c r="B47" s="5" t="n">
         <v>44021.29166666666</v>
       </c>
       <c r="C47" s="2" t="n">
@@ -5130,10 +5513,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="5" t="n">
         <v>44021.79166666666</v>
       </c>
-      <c r="B48" s="3" t="n">
+      <c r="B48" s="5" t="n">
         <v>44022.25</v>
       </c>
       <c r="C48" s="2" t="n">
@@ -5180,10 +5563,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="5" t="n">
         <v>44022.54166666666</v>
       </c>
-      <c r="B49" s="3" t="n">
+      <c r="B49" s="5" t="n">
         <v>44023.04166666666</v>
       </c>
       <c r="C49" s="2" t="n">
@@ -5230,10 +5613,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="5" t="n">
         <v>44024.625</v>
       </c>
-      <c r="B50" s="3" t="n">
+      <c r="B50" s="5" t="n">
         <v>44024.75</v>
       </c>
       <c r="C50" s="2" t="n">
@@ -5280,10 +5663,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="5" t="n">
         <v>44025.04166666666</v>
       </c>
-      <c r="B51" s="3" t="n">
+      <c r="B51" s="5" t="n">
         <v>44026.70833333334</v>
       </c>
       <c r="C51" s="2" t="n">
@@ -5330,10 +5713,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="5" t="n">
         <v>44027</v>
       </c>
-      <c r="B52" s="3" t="n">
+      <c r="B52" s="5" t="n">
         <v>44027.29166666666</v>
       </c>
       <c r="C52" s="2" t="n">
@@ -5380,10 +5763,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="5" t="n">
         <v>44028.79166666666</v>
       </c>
-      <c r="B53" s="3" t="n">
+      <c r="B53" s="5" t="n">
         <v>44028.875</v>
       </c>
       <c r="C53" s="2" t="n">
@@ -5430,10 +5813,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="5" t="n">
         <v>44030.70833333334</v>
       </c>
-      <c r="B54" s="3" t="n">
+      <c r="B54" s="5" t="n">
         <v>44030.875</v>
       </c>
       <c r="C54" s="2" t="n">
@@ -5480,10 +5863,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="5" t="n">
         <v>44033.375</v>
       </c>
-      <c r="B55" s="3" t="n">
+      <c r="B55" s="5" t="n">
         <v>44034.08333333334</v>
       </c>
       <c r="C55" s="2" t="n">
@@ -5530,10 +5913,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="5" t="n">
         <v>44034.66666666666</v>
       </c>
-      <c r="B56" s="3" t="n">
+      <c r="B56" s="5" t="n">
         <v>44035</v>
       </c>
       <c r="C56" s="2" t="n">
@@ -5580,10 +5963,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="5" t="n">
         <v>44039.29166666666</v>
       </c>
-      <c r="B57" s="3" t="n">
+      <c r="B57" s="5" t="n">
         <v>44039.58333333334</v>
       </c>
       <c r="C57" s="2" t="n">
@@ -5630,10 +6013,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="5" t="n">
         <v>44046.45833333334</v>
       </c>
-      <c r="B58" s="3" t="n">
+      <c r="B58" s="5" t="n">
         <v>44046.83333333334</v>
       </c>
       <c r="C58" s="2" t="n">
@@ -5680,10 +6063,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="5" t="n">
         <v>44048.45833333334</v>
       </c>
-      <c r="B59" s="3" t="n">
+      <c r="B59" s="5" t="n">
         <v>44048.54166666666</v>
       </c>
       <c r="C59" s="2" t="n">
@@ -5730,10 +6113,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="5" t="n">
         <v>44049.375</v>
       </c>
-      <c r="B60" s="3" t="n">
+      <c r="B60" s="5" t="n">
         <v>44049.75</v>
       </c>
       <c r="C60" s="2" t="n">
@@ -5780,10 +6163,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="5" t="n">
         <v>44073.29166666666</v>
       </c>
-      <c r="B61" s="3" t="n">
+      <c r="B61" s="5" t="n">
         <v>44073.83333333334</v>
       </c>
       <c r="C61" s="2" t="n">
@@ -5830,10 +6213,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="5" t="n">
         <v>44074.41666666666</v>
       </c>
-      <c r="B62" s="3" t="n">
+      <c r="B62" s="5" t="n">
         <v>44074.91666666666</v>
       </c>
       <c r="C62" s="2" t="n">
@@ -5880,10 +6263,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="5" t="n">
         <v>44075.04166666666</v>
       </c>
-      <c r="B63" s="3" t="n">
+      <c r="B63" s="5" t="n">
         <v>44075.125</v>
       </c>
       <c r="C63" s="2" t="n">
@@ -5930,10 +6313,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="5" t="n">
         <v>44076</v>
       </c>
-      <c r="B64" s="3" t="n">
+      <c r="B64" s="5" t="n">
         <v>44076.25</v>
       </c>
       <c r="C64" s="2" t="n">
@@ -5980,10 +6363,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="5" t="n">
         <v>44076.375</v>
       </c>
-      <c r="B65" s="3" t="n">
+      <c r="B65" s="5" t="n">
         <v>44076.79166666666</v>
       </c>
       <c r="C65" s="2" t="n">
@@ -6030,10 +6413,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="5" t="n">
         <v>44082.04166666666</v>
       </c>
-      <c r="B66" s="3" t="n">
+      <c r="B66" s="5" t="n">
         <v>44082.91666666666</v>
       </c>
       <c r="C66" s="2" t="n">
@@ -6080,10 +6463,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="5" t="n">
         <v>44091</v>
       </c>
-      <c r="B67" s="3" t="n">
+      <c r="B67" s="5" t="n">
         <v>44091.125</v>
       </c>
       <c r="C67" s="2" t="n">
@@ -6130,10 +6513,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="5" t="n">
         <v>44091.33333333334</v>
       </c>
-      <c r="B68" s="3" t="n">
+      <c r="B68" s="5" t="n">
         <v>44091.70833333334</v>
       </c>
       <c r="C68" s="2" t="n">
@@ -6180,10 +6563,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="n">
+      <c r="A69" s="5" t="n">
         <v>44092</v>
       </c>
-      <c r="B69" s="3" t="n">
+      <c r="B69" s="5" t="n">
         <v>44092.25</v>
       </c>
       <c r="C69" s="2" t="n">
@@ -6230,10 +6613,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="n">
+      <c r="A70" s="5" t="n">
         <v>44099.375</v>
       </c>
-      <c r="B70" s="3" t="n">
+      <c r="B70" s="5" t="n">
         <v>44099.95833333334</v>
       </c>
       <c r="C70" s="2" t="n">
@@ -6280,10 +6663,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="n">
+      <c r="A71" s="5" t="n">
         <v>44102.45833333334</v>
       </c>
-      <c r="B71" s="3" t="n">
+      <c r="B71" s="5" t="n">
         <v>44103.58333333334</v>
       </c>
       <c r="C71" s="2" t="n">
@@ -6330,10 +6713,10 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="3" t="n">
+      <c r="A72" s="5" t="n">
         <v>44103.95833333334</v>
       </c>
-      <c r="B72" s="3" t="n">
+      <c r="B72" s="5" t="n">
         <v>44104.125</v>
       </c>
       <c r="C72" s="2" t="n">
@@ -6380,10 +6763,10 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="3" t="n">
+      <c r="A73" s="5" t="n">
         <v>44105.54166666666</v>
       </c>
-      <c r="B73" s="3" t="n">
+      <c r="B73" s="5" t="n">
         <v>44105.83333333334</v>
       </c>
       <c r="C73" s="2" t="n">
@@ -6430,10 +6813,10 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="3" t="n">
+      <c r="A74" s="5" t="n">
         <v>44106</v>
       </c>
-      <c r="B74" s="3" t="n">
+      <c r="B74" s="5" t="n">
         <v>44106.66666666666</v>
       </c>
       <c r="C74" s="2" t="n">
@@ -6480,10 +6863,10 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="3" t="n">
+      <c r="A75" s="5" t="n">
         <v>44116.375</v>
       </c>
-      <c r="B75" s="3" t="n">
+      <c r="B75" s="5" t="n">
         <v>44116.58333333334</v>
       </c>
       <c r="C75" s="2" t="n">
@@ -6530,10 +6913,10 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="3" t="n">
+      <c r="A76" s="5" t="n">
         <v>44117.33333333334</v>
       </c>
-      <c r="B76" s="3" t="n">
+      <c r="B76" s="5" t="n">
         <v>44118</v>
       </c>
       <c r="C76" s="2" t="n">
@@ -6580,10 +6963,10 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="3" t="n">
+      <c r="A77" s="5" t="n">
         <v>44121.29166666666</v>
       </c>
-      <c r="B77" s="3" t="n">
+      <c r="B77" s="5" t="n">
         <v>44121.875</v>
       </c>
       <c r="C77" s="2" t="n">
@@ -6630,10 +7013,10 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="3" t="n">
+      <c r="A78" s="5" t="n">
         <v>44123.16666666666</v>
       </c>
-      <c r="B78" s="3" t="n">
+      <c r="B78" s="5" t="n">
         <v>44123.91666666666</v>
       </c>
       <c r="C78" s="2" t="n">
@@ -6680,10 +7063,10 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="3" t="n">
+      <c r="A79" s="5" t="n">
         <v>44124.20833333334</v>
       </c>
-      <c r="B79" s="3" t="n">
+      <c r="B79" s="5" t="n">
         <v>44124.79166666666</v>
       </c>
       <c r="C79" s="2" t="n">
@@ -6730,10 +7113,10 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="3" t="n">
+      <c r="A80" s="5" t="n">
         <v>44126.625</v>
       </c>
-      <c r="B80" s="3" t="n">
+      <c r="B80" s="5" t="n">
         <v>44126.83333333334</v>
       </c>
       <c r="C80" s="2" t="n">
@@ -6780,10 +7163,10 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="3" t="n">
+      <c r="A81" s="5" t="n">
         <v>44127.375</v>
       </c>
-      <c r="B81" s="3" t="n">
+      <c r="B81" s="5" t="n">
         <v>44128.125</v>
       </c>
       <c r="C81" s="2" t="n">
@@ -6830,10 +7213,10 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="3" t="n">
+      <c r="A82" s="5" t="n">
         <v>44128.79166666666</v>
       </c>
-      <c r="B82" s="3" t="n">
+      <c r="B82" s="5" t="n">
         <v>44128.91666666666</v>
       </c>
       <c r="C82" s="2" t="n">
@@ -6880,10 +7263,10 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="3" t="n">
+      <c r="A83" s="5" t="n">
         <v>44166.33333333334</v>
       </c>
-      <c r="B83" s="3" t="n">
+      <c r="B83" s="5" t="n">
         <v>44167</v>
       </c>
       <c r="C83" s="2" t="n">
@@ -6930,10 +7313,10 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="3" t="n">
+      <c r="A84" s="5" t="n">
         <v>44176.125</v>
       </c>
-      <c r="B84" s="3" t="n">
+      <c r="B84" s="5" t="n">
         <v>44178.75</v>
       </c>
       <c r="C84" s="2" t="n">
@@ -6980,10 +7363,10 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="3" t="n">
+      <c r="A85" s="5" t="n">
         <v>44179.375</v>
       </c>
-      <c r="B85" s="3" t="n">
+      <c r="B85" s="5" t="n">
         <v>44179.91666666666</v>
       </c>
       <c r="C85" s="2" t="n">
@@ -7030,10 +7413,10 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="3" t="n">
+      <c r="A86" s="5" t="n">
         <v>44182.83333333334</v>
       </c>
-      <c r="B86" s="3" t="n">
+      <c r="B86" s="5" t="n">
         <v>44183.16666666666</v>
       </c>
       <c r="C86" s="2" t="n">
@@ -7080,10 +7463,10 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="3" t="n">
+      <c r="A87" s="5" t="n">
         <v>44189.125</v>
       </c>
-      <c r="B87" s="3" t="n">
+      <c r="B87" s="5" t="n">
         <v>44189.79166666666</v>
       </c>
       <c r="C87" s="2" t="n">
@@ -7130,10 +7513,10 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="3" t="n">
+      <c r="A88" s="5" t="n">
         <v>44192.5</v>
       </c>
-      <c r="B88" s="3" t="n">
+      <c r="B88" s="5" t="n">
         <v>44192.95833333334</v>
       </c>
       <c r="C88" s="2" t="n">
@@ -7180,10 +7563,10 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="3" t="n">
+      <c r="A89" s="5" t="n">
         <v>44196.33333333334</v>
       </c>
-      <c r="B89" s="3" t="n">
+      <c r="B89" s="5" t="n">
         <v>44196.75</v>
       </c>
       <c r="C89" s="2" t="n">
@@ -7230,10 +7613,10 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="3" t="n">
+      <c r="A90" s="5" t="n">
         <v>44196.875</v>
       </c>
-      <c r="B90" s="3" t="n">
+      <c r="B90" s="5" t="n">
         <v>44197.16666666666</v>
       </c>
       <c r="C90" s="2" t="n">
@@ -7280,10 +7663,10 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="3" t="n">
+      <c r="A91" s="5" t="n">
         <v>44201.29166666666</v>
       </c>
-      <c r="B91" s="3" t="n">
+      <c r="B91" s="5" t="n">
         <v>44201.70833333334</v>
       </c>
       <c r="C91" s="2" t="n">
@@ -7330,10 +7713,10 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="3" t="n">
+      <c r="A92" s="5" t="n">
         <v>44202.375</v>
       </c>
-      <c r="B92" s="3" t="n">
+      <c r="B92" s="5" t="n">
         <v>44202.91666666666</v>
       </c>
       <c r="C92" s="2" t="n">
@@ -7380,10 +7763,10 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="3" t="n">
+      <c r="A93" s="5" t="n">
         <v>44203.33333333334</v>
       </c>
-      <c r="B93" s="3" t="n">
+      <c r="B93" s="5" t="n">
         <v>44203.54166666666</v>
       </c>
       <c r="C93" s="2" t="n">
@@ -7430,10 +7813,10 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="3" t="n">
+      <c r="A94" s="5" t="n">
         <v>44204.125</v>
       </c>
-      <c r="B94" s="3" t="n">
+      <c r="B94" s="5" t="n">
         <v>44204.45833333334</v>
       </c>
       <c r="C94" s="2" t="n">
@@ -7480,10 +7863,10 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="3" t="n">
+      <c r="A95" s="5" t="n">
         <v>44205.29166666666</v>
       </c>
-      <c r="B95" s="3" t="n">
+      <c r="B95" s="5" t="n">
         <v>44205.58333333334</v>
       </c>
       <c r="C95" s="2" t="n">
@@ -7530,10 +7913,10 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="3" t="n">
+      <c r="A96" s="5" t="n">
         <v>44207.95833333334</v>
       </c>
-      <c r="B96" s="3" t="n">
+      <c r="B96" s="5" t="n">
         <v>44208.16666666666</v>
       </c>
       <c r="C96" s="2" t="n">
@@ -7580,10 +7963,10 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="3" t="n">
+      <c r="A97" s="5" t="n">
         <v>44209.33333333334</v>
       </c>
-      <c r="B97" s="3" t="n">
+      <c r="B97" s="5" t="n">
         <v>44209.54166666666</v>
       </c>
       <c r="C97" s="2" t="n">
@@ -7630,10 +8013,10 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="3" t="n">
+      <c r="A98" s="5" t="n">
         <v>44209.95833333334</v>
       </c>
-      <c r="B98" s="3" t="n">
+      <c r="B98" s="5" t="n">
         <v>44210.41666666666</v>
       </c>
       <c r="C98" s="2" t="n">
@@ -7680,10 +8063,10 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="3" t="n">
+      <c r="A99" s="5" t="n">
         <v>44218.08333333334</v>
       </c>
-      <c r="B99" s="3" t="n">
+      <c r="B99" s="5" t="n">
         <v>44218.75</v>
       </c>
       <c r="C99" s="2" t="n">
@@ -7730,10 +8113,10 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="3" t="n">
+      <c r="A100" s="5" t="n">
         <v>44219.625</v>
       </c>
-      <c r="B100" s="3" t="n">
+      <c r="B100" s="5" t="n">
         <v>44220.08333333334</v>
       </c>
       <c r="C100" s="2" t="n">
@@ -7780,10 +8163,10 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="3" t="n">
+      <c r="A101" s="5" t="n">
         <v>44221.25</v>
       </c>
-      <c r="B101" s="3" t="n">
+      <c r="B101" s="5" t="n">
         <v>44221.58333333334</v>
       </c>
       <c r="C101" s="2" t="n">
@@ -7830,10 +8213,10 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="3" t="n">
+      <c r="A102" s="5" t="n">
         <v>44224.29166666666</v>
       </c>
-      <c r="B102" s="3" t="n">
+      <c r="B102" s="5" t="n">
         <v>44224.625</v>
       </c>
       <c r="C102" s="2" t="n">
@@ -7880,10 +8263,10 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="3" t="n">
+      <c r="A103" s="5" t="n">
         <v>44225.66666666666</v>
       </c>
-      <c r="B103" s="3" t="n">
+      <c r="B103" s="5" t="n">
         <v>44225.91666666666</v>
       </c>
       <c r="C103" s="2" t="n">
@@ -7930,10 +8313,10 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="3" t="n">
+      <c r="A104" s="5" t="n">
         <v>44226.54166666666</v>
       </c>
-      <c r="B104" s="3" t="n">
+      <c r="B104" s="5" t="n">
         <v>44226.83333333334</v>
       </c>
       <c r="C104" s="2" t="n">
@@ -7980,10 +8363,10 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="3" t="n">
+      <c r="A105" s="5" t="n">
         <v>44226.95833333334</v>
       </c>
-      <c r="B105" s="3" t="n">
+      <c r="B105" s="5" t="n">
         <v>44227.5</v>
       </c>
       <c r="C105" s="2" t="n">
@@ -8030,10 +8413,10 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="3" t="n">
+      <c r="A106" s="5" t="n">
         <v>44227.625</v>
       </c>
-      <c r="B106" s="3" t="n">
+      <c r="B106" s="5" t="n">
         <v>44227.83333333334</v>
       </c>
       <c r="C106" s="2" t="n">
@@ -8080,10 +8463,10 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="3" t="n">
+      <c r="A107" s="5" t="n">
         <v>44228</v>
       </c>
-      <c r="B107" s="3" t="n">
+      <c r="B107" s="5" t="n">
         <v>44228.20833333334</v>
       </c>
       <c r="C107" s="2" t="n">
@@ -8130,10 +8513,10 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="3" t="n">
+      <c r="A108" s="5" t="n">
         <v>44229.08333333334</v>
       </c>
-      <c r="B108" s="3" t="n">
+      <c r="B108" s="5" t="n">
         <v>44229.33333333334</v>
       </c>
       <c r="C108" s="2" t="n">
@@ -8180,10 +8563,10 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="3" t="n">
+      <c r="A109" s="5" t="n">
         <v>44230.41666666666</v>
       </c>
-      <c r="B109" s="3" t="n">
+      <c r="B109" s="5" t="n">
         <v>44230.83333333334</v>
       </c>
       <c r="C109" s="2" t="n">
@@ -8230,10 +8613,10 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="3" t="n">
+      <c r="A110" s="5" t="n">
         <v>44230.95833333334</v>
       </c>
-      <c r="B110" s="3" t="n">
+      <c r="B110" s="5" t="n">
         <v>44231.16666666666</v>
       </c>
       <c r="C110" s="2" t="n">
@@ -8280,10 +8663,10 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="3" t="n">
+      <c r="A111" s="5" t="n">
         <v>44231.75</v>
       </c>
-      <c r="B111" s="3" t="n">
+      <c r="B111" s="5" t="n">
         <v>44231.91666666666</v>
       </c>
       <c r="C111" s="2" t="n">
@@ -8330,10 +8713,10 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="3" t="n">
+      <c r="A112" s="5" t="n">
         <v>44232.04166666666</v>
       </c>
-      <c r="B112" s="3" t="n">
+      <c r="B112" s="5" t="n">
         <v>44232.41666666666</v>
       </c>
       <c r="C112" s="2" t="n">
@@ -8380,10 +8763,10 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="3" t="n">
+      <c r="A113" s="5" t="n">
         <v>44232.54166666666</v>
       </c>
-      <c r="B113" s="3" t="n">
+      <c r="B113" s="5" t="n">
         <v>44233</v>
       </c>
       <c r="C113" s="2" t="n">
@@ -8430,10 +8813,10 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="3" t="n">
+      <c r="A114" s="5" t="n">
         <v>44233.91666666666</v>
       </c>
-      <c r="B114" s="3" t="n">
+      <c r="B114" s="5" t="n">
         <v>44234</v>
       </c>
       <c r="C114" s="2" t="n">
@@ -8480,10 +8863,10 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="3" t="n">
+      <c r="A115" s="5" t="n">
         <v>44234.83333333334</v>
       </c>
-      <c r="B115" s="3" t="n">
+      <c r="B115" s="5" t="n">
         <v>44235.16666666666</v>
       </c>
       <c r="C115" s="2" t="n">
@@ -8530,10 +8913,10 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="3" t="n">
+      <c r="A116" s="5" t="n">
         <v>44236</v>
       </c>
-      <c r="B116" s="3" t="n">
+      <c r="B116" s="5" t="n">
         <v>44236.54166666666</v>
       </c>
       <c r="C116" s="2" t="n">
@@ -8580,10 +8963,10 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="3" t="n">
+      <c r="A117" s="5" t="n">
         <v>44237.08333333334</v>
       </c>
-      <c r="B117" s="3" t="n">
+      <c r="B117" s="5" t="n">
         <v>44238.25</v>
       </c>
       <c r="C117" s="2" t="n">
@@ -8630,10 +9013,10 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="3" t="n">
+      <c r="A118" s="5" t="n">
         <v>44243.08333333334</v>
       </c>
-      <c r="B118" s="3" t="n">
+      <c r="B118" s="5" t="n">
         <v>44243.29166666666</v>
       </c>
       <c r="C118" s="2" t="n">
@@ -8680,10 +9063,10 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="3" t="n">
+      <c r="A119" s="5" t="n">
         <v>44245.41666666666</v>
       </c>
-      <c r="B119" s="3" t="n">
+      <c r="B119" s="5" t="n">
         <v>44246.08333333334</v>
       </c>
       <c r="C119" s="2" t="n">
@@ -8730,10 +9113,10 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="3" t="n">
+      <c r="A120" s="5" t="n">
         <v>44246.25</v>
       </c>
-      <c r="B120" s="3" t="n">
+      <c r="B120" s="5" t="n">
         <v>44246.875</v>
       </c>
       <c r="C120" s="2" t="n">
@@ -8780,10 +9163,10 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="3" t="n">
+      <c r="A121" s="5" t="n">
         <v>44254.91666666666</v>
       </c>
-      <c r="B121" s="3" t="n">
+      <c r="B121" s="5" t="n">
         <v>44255.75</v>
       </c>
       <c r="C121" s="2" t="n">
@@ -8830,10 +9213,10 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="3" t="n">
+      <c r="A122" s="5" t="n">
         <v>44276.29166666666</v>
       </c>
-      <c r="B122" s="3" t="n">
+      <c r="B122" s="5" t="n">
         <v>44276.75</v>
       </c>
       <c r="C122" s="2" t="n">
@@ -8880,10 +9263,10 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="3" t="n">
+      <c r="A123" s="5" t="n">
         <v>44278.45833333334</v>
       </c>
-      <c r="B123" s="3" t="n">
+      <c r="B123" s="5" t="n">
         <v>44279.08333333334</v>
       </c>
       <c r="C123" s="2" t="n">
@@ -8930,10 +9313,10 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="3" t="n">
+      <c r="A124" s="5" t="n">
         <v>44282.08333333334</v>
       </c>
-      <c r="B124" s="3" t="n">
+      <c r="B124" s="5" t="n">
         <v>44282.66666666666</v>
       </c>
       <c r="C124" s="2" t="n">
@@ -8980,10 +9363,10 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="3" t="n">
+      <c r="A125" s="5" t="n">
         <v>44286.58333333334</v>
       </c>
-      <c r="B125" s="3" t="n">
+      <c r="B125" s="5" t="n">
         <v>44286.79166666666</v>
       </c>
       <c r="C125" s="2" t="n">
@@ -9030,10 +9413,10 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="3" t="n">
+      <c r="A126" s="5" t="n">
         <v>44287.25</v>
       </c>
-      <c r="B126" s="3" t="n">
+      <c r="B126" s="5" t="n">
         <v>44287.75</v>
       </c>
       <c r="C126" s="2" t="n">
@@ -9080,10 +9463,10 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="3" t="n">
+      <c r="A127" s="5" t="n">
         <v>44299.375</v>
       </c>
-      <c r="B127" s="3" t="n">
+      <c r="B127" s="5" t="n">
         <v>44299.75</v>
       </c>
       <c r="C127" s="2" t="n">
@@ -9130,10 +9513,10 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="3" t="n">
+      <c r="A128" s="5" t="n">
         <v>44302.25</v>
       </c>
-      <c r="B128" s="3" t="n">
+      <c r="B128" s="5" t="n">
         <v>44302.54166666666</v>
       </c>
       <c r="C128" s="2" t="n">
@@ -9180,10 +9563,10 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="3" t="n">
+      <c r="A129" s="5" t="n">
         <v>44330.375</v>
       </c>
-      <c r="B129" s="3" t="n">
+      <c r="B129" s="5" t="n">
         <v>44330.70833333334</v>
       </c>
       <c r="C129" s="2" t="n">
@@ -9230,10 +9613,10 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="3" t="n">
+      <c r="A130" s="5" t="n">
         <v>44336.16666666666</v>
       </c>
-      <c r="B130" s="3" t="n">
+      <c r="B130" s="5" t="n">
         <v>44336.54166666666</v>
       </c>
       <c r="C130" s="2" t="n">
@@ -9280,10 +9663,10 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="3" t="n">
+      <c r="A131" s="5" t="n">
         <v>44345.54166666666</v>
       </c>
-      <c r="B131" s="3" t="n">
+      <c r="B131" s="5" t="n">
         <v>44345.91666666666</v>
       </c>
       <c r="C131" s="2" t="n">
@@ -9330,10 +9713,10 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="3" t="n">
+      <c r="A132" s="5" t="n">
         <v>44348.41666666666</v>
       </c>
-      <c r="B132" s="3" t="n">
+      <c r="B132" s="5" t="n">
         <v>44349</v>
       </c>
       <c r="C132" s="2" t="n">
@@ -9380,10 +9763,10 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="3" t="n">
+      <c r="A133" s="5" t="n">
         <v>44352.33333333334</v>
       </c>
-      <c r="B133" s="3" t="n">
+      <c r="B133" s="5" t="n">
         <v>44352.79166666666</v>
       </c>
       <c r="C133" s="2" t="n">
@@ -9430,10 +9813,10 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="3" t="n">
+      <c r="A134" s="5" t="n">
         <v>44353.20833333334</v>
       </c>
-      <c r="B134" s="3" t="n">
+      <c r="B134" s="5" t="n">
         <v>44353.41666666666</v>
       </c>
       <c r="C134" s="2" t="n">
@@ -9480,10 +9863,10 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="3" t="n">
+      <c r="A135" s="5" t="n">
         <v>44354.33333333334</v>
       </c>
-      <c r="B135" s="3" t="n">
+      <c r="B135" s="5" t="n">
         <v>44354.79166666666</v>
       </c>
       <c r="C135" s="2" t="n">
@@ -9530,10 +9913,10 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="3" t="n">
+      <c r="A136" s="5" t="n">
         <v>44354.91666666666</v>
       </c>
-      <c r="B136" s="3" t="n">
+      <c r="B136" s="5" t="n">
         <v>44355.66666666666</v>
       </c>
       <c r="C136" s="2" t="n">
@@ -9580,10 +9963,10 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="3" t="n">
+      <c r="A137" s="5" t="n">
         <v>44359.25</v>
       </c>
-      <c r="B137" s="3" t="n">
+      <c r="B137" s="5" t="n">
         <v>44359.54166666666</v>
       </c>
       <c r="C137" s="2" t="n">
@@ -9630,10 +10013,10 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="3" t="n">
+      <c r="A138" s="5" t="n">
         <v>44359.70833333334</v>
       </c>
-      <c r="B138" s="3" t="n">
+      <c r="B138" s="5" t="n">
         <v>44360.04166666666</v>
       </c>
       <c r="C138" s="2" t="n">
@@ -9680,10 +10063,10 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="3" t="n">
+      <c r="A139" s="5" t="n">
         <v>44360.20833333334</v>
       </c>
-      <c r="B139" s="3" t="n">
+      <c r="B139" s="5" t="n">
         <v>44360.625</v>
       </c>
       <c r="C139" s="2" t="n">
@@ -9730,10 +10113,10 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="3" t="n">
+      <c r="A140" s="5" t="n">
         <v>44365.33333333334</v>
       </c>
-      <c r="B140" s="3" t="n">
+      <c r="B140" s="5" t="n">
         <v>44365.70833333334</v>
       </c>
       <c r="C140" s="2" t="n">
@@ -9780,10 +10163,10 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="3" t="n">
+      <c r="A141" s="5" t="n">
         <v>44366.66666666666</v>
       </c>
-      <c r="B141" s="3" t="n">
+      <c r="B141" s="5" t="n">
         <v>44367.41666666666</v>
       </c>
       <c r="C141" s="2" t="n">
@@ -9830,10 +10213,10 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="3" t="n">
+      <c r="A142" s="5" t="n">
         <v>44370.70833333334</v>
       </c>
-      <c r="B142" s="3" t="n">
+      <c r="B142" s="5" t="n">
         <v>44371.16666666666</v>
       </c>
       <c r="C142" s="2" t="n">
@@ -9880,10 +10263,10 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="3" t="n">
+      <c r="A143" s="5" t="n">
         <v>44371.33333333334</v>
       </c>
-      <c r="B143" s="3" t="n">
+      <c r="B143" s="5" t="n">
         <v>44371.79166666666</v>
       </c>
       <c r="C143" s="2" t="n">
@@ -9930,10 +10313,10 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="3" t="n">
+      <c r="A144" s="5" t="n">
         <v>44372.25</v>
       </c>
-      <c r="B144" s="3" t="n">
+      <c r="B144" s="5" t="n">
         <v>44372.375</v>
       </c>
       <c r="C144" s="2" t="n">
@@ -9980,10 +10363,10 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="3" t="n">
+      <c r="A145" s="5" t="n">
         <v>44376.5</v>
       </c>
-      <c r="B145" s="3" t="n">
+      <c r="B145" s="5" t="n">
         <v>44377.16666666666</v>
       </c>
       <c r="C145" s="2" t="n">
@@ -10030,10 +10413,10 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="3" t="n">
+      <c r="A146" s="5" t="n">
         <v>44377.79166666666</v>
       </c>
-      <c r="B146" s="3" t="n">
+      <c r="B146" s="5" t="n">
         <v>44378.04166666666</v>
       </c>
       <c r="C146" s="2" t="n">
@@ -10080,10 +10463,10 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="3" t="n">
+      <c r="A147" s="5" t="n">
         <v>44379.33333333334</v>
       </c>
-      <c r="B147" s="3" t="n">
+      <c r="B147" s="5" t="n">
         <v>44379.75</v>
       </c>
       <c r="C147" s="2" t="n">
@@ -10130,10 +10513,10 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="3" t="n">
+      <c r="A148" s="5" t="n">
         <v>44379.875</v>
       </c>
-      <c r="B148" s="3" t="n">
+      <c r="B148" s="5" t="n">
         <v>44380.20833333334</v>
       </c>
       <c r="C148" s="2" t="n">
@@ -10180,10 +10563,10 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="3" t="n">
+      <c r="A149" s="5" t="n">
         <v>44381.375</v>
       </c>
-      <c r="B149" s="3" t="n">
+      <c r="B149" s="5" t="n">
         <v>44381.625</v>
       </c>
       <c r="C149" s="2" t="n">
@@ -10230,10 +10613,10 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="3" t="n">
+      <c r="A150" s="5" t="n">
         <v>44384.54166666666</v>
       </c>
-      <c r="B150" s="3" t="n">
+      <c r="B150" s="5" t="n">
         <v>44384.79166666666</v>
       </c>
       <c r="C150" s="2" t="n">
@@ -10280,10 +10663,10 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="3" t="n">
+      <c r="A151" s="5" t="n">
         <v>44386.08333333334</v>
       </c>
-      <c r="B151" s="3" t="n">
+      <c r="B151" s="5" t="n">
         <v>44386.75</v>
       </c>
       <c r="C151" s="2" t="n">
@@ -10330,10 +10713,10 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="3" t="n">
+      <c r="A152" s="5" t="n">
         <v>44388.75</v>
       </c>
-      <c r="B152" s="3" t="n">
+      <c r="B152" s="5" t="n">
         <v>44389.58333333334</v>
       </c>
       <c r="C152" s="2" t="n">
@@ -10380,10 +10763,10 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="3" t="n">
+      <c r="A153" s="5" t="n">
         <v>44389.95833333334</v>
       </c>
-      <c r="B153" s="3" t="n">
+      <c r="B153" s="5" t="n">
         <v>44390.29166666666</v>
       </c>
       <c r="C153" s="2" t="n">
@@ -10430,10 +10813,10 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="3" t="n">
+      <c r="A154" s="5" t="n">
         <v>44390.41666666666</v>
       </c>
-      <c r="B154" s="3" t="n">
+      <c r="B154" s="5" t="n">
         <v>44391.16666666666</v>
       </c>
       <c r="C154" s="2" t="n">
@@ -10480,10 +10863,10 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="3" t="n">
+      <c r="A155" s="5" t="n">
         <v>44391.58333333334</v>
       </c>
-      <c r="B155" s="3" t="n">
+      <c r="B155" s="5" t="n">
         <v>44391.75</v>
       </c>
       <c r="C155" s="2" t="n">
@@ -10530,10 +10913,10 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="3" t="n">
+      <c r="A156" s="5" t="n">
         <v>44397.20833333334</v>
       </c>
-      <c r="B156" s="3" t="n">
+      <c r="B156" s="5" t="n">
         <v>44397.83333333334</v>
       </c>
       <c r="C156" s="2" t="n">
@@ -10580,10 +10963,10 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="3" t="n">
+      <c r="A157" s="5" t="n">
         <v>44403.45833333334</v>
       </c>
-      <c r="B157" s="3" t="n">
+      <c r="B157" s="5" t="n">
         <v>44404.08333333334</v>
       </c>
       <c r="C157" s="2" t="n">
@@ -10630,10 +11013,10 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="3" t="n">
+      <c r="A158" s="5" t="n">
         <v>44404.33333333334</v>
       </c>
-      <c r="B158" s="3" t="n">
+      <c r="B158" s="5" t="n">
         <v>44405.125</v>
       </c>
       <c r="C158" s="2" t="n">
@@ -10680,10 +11063,10 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="3" t="n">
+      <c r="A159" s="5" t="n">
         <v>44407.54166666666</v>
       </c>
-      <c r="B159" s="3" t="n">
+      <c r="B159" s="5" t="n">
         <v>44407.91666666666</v>
       </c>
       <c r="C159" s="2" t="n">
@@ -10730,10 +11113,10 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="3" t="n">
+      <c r="A160" s="5" t="n">
         <v>44410.625</v>
       </c>
-      <c r="B160" s="3" t="n">
+      <c r="B160" s="5" t="n">
         <v>44411.125</v>
       </c>
       <c r="C160" s="2" t="n">
@@ -10780,10 +11163,10 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="3" t="n">
+      <c r="A161" s="5" t="n">
         <v>44411.29166666666</v>
       </c>
-      <c r="B161" s="3" t="n">
+      <c r="B161" s="5" t="n">
         <v>44412.29166666666</v>
       </c>
       <c r="C161" s="2" t="n">
@@ -10830,10 +11213,10 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="3" t="n">
+      <c r="A162" s="5" t="n">
         <v>44412.41666666666</v>
       </c>
-      <c r="B162" s="3" t="n">
+      <c r="B162" s="5" t="n">
         <v>44412.54166666666</v>
       </c>
       <c r="C162" s="2" t="n">
@@ -10880,10 +11263,10 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="3" t="n">
+      <c r="A163" s="5" t="n">
         <v>44414.20833333334</v>
       </c>
-      <c r="B163" s="3" t="n">
+      <c r="B163" s="5" t="n">
         <v>44415.16666666666</v>
       </c>
       <c r="C163" s="2" t="n">
@@ -10930,10 +11313,10 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="3" t="n">
+      <c r="A164" s="5" t="n">
         <v>44415.54166666666</v>
       </c>
-      <c r="B164" s="3" t="n">
+      <c r="B164" s="5" t="n">
         <v>44416</v>
       </c>
       <c r="C164" s="2" t="n">
@@ -10980,10 +11363,10 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="3" t="n">
+      <c r="A165" s="5" t="n">
         <v>44416.5</v>
       </c>
-      <c r="B165" s="3" t="n">
+      <c r="B165" s="5" t="n">
         <v>44416.58333333334</v>
       </c>
       <c r="C165" s="2" t="n">
@@ -11030,10 +11413,10 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="3" t="n">
+      <c r="A166" s="5" t="n">
         <v>44416.875</v>
       </c>
-      <c r="B166" s="3" t="n">
+      <c r="B166" s="5" t="n">
         <v>44417.54166666666</v>
       </c>
       <c r="C166" s="2" t="n">
@@ -11080,10 +11463,10 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="3" t="n">
+      <c r="A167" s="5" t="n">
         <v>44422.16666666666</v>
       </c>
-      <c r="B167" s="3" t="n">
+      <c r="B167" s="5" t="n">
         <v>44422.91666666666</v>
       </c>
       <c r="C167" s="2" t="n">
@@ -11130,10 +11513,10 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="3" t="n">
+      <c r="A168" s="5" t="n">
         <v>44423.16666666666</v>
       </c>
-      <c r="B168" s="3" t="n">
+      <c r="B168" s="5" t="n">
         <v>44423.95833333334</v>
       </c>
       <c r="C168" s="2" t="n">
@@ -11180,10 +11563,10 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="3" t="n">
+      <c r="A169" s="5" t="n">
         <v>44424.66666666666</v>
       </c>
-      <c r="B169" s="3" t="n">
+      <c r="B169" s="5" t="n">
         <v>44424.79166666666</v>
       </c>
       <c r="C169" s="2" t="n">
@@ -11230,10 +11613,10 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="3" t="n">
+      <c r="A170" s="5" t="n">
         <v>44428.125</v>
       </c>
-      <c r="B170" s="3" t="n">
+      <c r="B170" s="5" t="n">
         <v>44429.375</v>
       </c>
       <c r="C170" s="2" t="n">
@@ -11280,10 +11663,10 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="3" t="n">
+      <c r="A171" s="5" t="n">
         <v>44429.875</v>
       </c>
-      <c r="B171" s="3" t="n">
+      <c r="B171" s="5" t="n">
         <v>44430.625</v>
       </c>
       <c r="C171" s="2" t="n">
@@ -11330,10 +11713,10 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="3" t="n">
+      <c r="A172" s="5" t="n">
         <v>44433.125</v>
       </c>
-      <c r="B172" s="3" t="n">
+      <c r="B172" s="5" t="n">
         <v>44433.79166666666</v>
       </c>
       <c r="C172" s="2" t="n">
@@ -11380,10 +11763,10 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="3" t="n">
+      <c r="A173" s="5" t="n">
         <v>44434</v>
       </c>
-      <c r="B173" s="3" t="n">
+      <c r="B173" s="5" t="n">
         <v>44434.75</v>
       </c>
       <c r="C173" s="2" t="n">
@@ -11430,10 +11813,10 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="3" t="n">
+      <c r="A174" s="5" t="n">
         <v>44445.33333333334</v>
       </c>
-      <c r="B174" s="3" t="n">
+      <c r="B174" s="5" t="n">
         <v>44445.58333333334</v>
       </c>
       <c r="C174" s="2" t="n">
@@ -11480,10 +11863,10 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="3" t="n">
+      <c r="A175" s="5" t="n">
         <v>44453.33333333334</v>
       </c>
-      <c r="B175" s="3" t="n">
+      <c r="B175" s="5" t="n">
         <v>44453.54166666666</v>
       </c>
       <c r="C175" s="2" t="n">
@@ -11530,10 +11913,10 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="3" t="n">
+      <c r="A176" s="5" t="n">
         <v>44466.08333333334</v>
       </c>
-      <c r="B176" s="3" t="n">
+      <c r="B176" s="5" t="n">
         <v>44466.5</v>
       </c>
       <c r="C176" s="2" t="n">
@@ -11580,10 +11963,10 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="3" t="n">
+      <c r="A177" s="5" t="n">
         <v>44469.5</v>
       </c>
-      <c r="B177" s="3" t="n">
+      <c r="B177" s="5" t="n">
         <v>44469.58333333334</v>
       </c>
       <c r="C177" s="2" t="n">
@@ -11630,10 +12013,10 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="3" t="n">
+      <c r="A178" s="5" t="n">
         <v>44471.66666666666</v>
       </c>
-      <c r="B178" s="3" t="n">
+      <c r="B178" s="5" t="n">
         <v>44472.25</v>
       </c>
       <c r="C178" s="2" t="n">
@@ -11680,10 +12063,10 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="3" t="n">
+      <c r="A179" s="5" t="n">
         <v>44484.25</v>
       </c>
-      <c r="B179" s="3" t="n">
+      <c r="B179" s="5" t="n">
         <v>44484.70833333334</v>
       </c>
       <c r="C179" s="2" t="n">
@@ -11730,10 +12113,10 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="3" t="n">
+      <c r="A180" s="5" t="n">
         <v>44492.95833333334</v>
       </c>
-      <c r="B180" s="3" t="n">
+      <c r="B180" s="5" t="n">
         <v>44493.04166666666</v>
       </c>
       <c r="C180" s="2" t="n">
@@ -11780,10 +12163,10 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="3" t="n">
+      <c r="A181" s="5" t="n">
         <v>44501.41666666666</v>
       </c>
-      <c r="B181" s="3" t="n">
+      <c r="B181" s="5" t="n">
         <v>44501.79166666666</v>
       </c>
       <c r="C181" s="2" t="n">
@@ -11830,10 +12213,10 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="3" t="n">
+      <c r="A182" s="5" t="n">
         <v>44503.45833333334</v>
       </c>
-      <c r="B182" s="3" t="n">
+      <c r="B182" s="5" t="n">
         <v>44503.70833333334</v>
       </c>
       <c r="C182" s="2" t="n">
@@ -11880,10 +12263,10 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="3" t="n">
+      <c r="A183" s="5" t="n">
         <v>44505.33333333334</v>
       </c>
-      <c r="B183" s="3" t="n">
+      <c r="B183" s="5" t="n">
         <v>44505.91666666666</v>
       </c>
       <c r="C183" s="2" t="n">
@@ -11930,10 +12313,10 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="3" t="n">
+      <c r="A184" s="5" t="n">
         <v>44517</v>
       </c>
-      <c r="B184" s="3" t="n">
+      <c r="B184" s="5" t="n">
         <v>44517.66666666666</v>
       </c>
       <c r="C184" s="2" t="n">
@@ -11980,10 +12363,10 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="3" t="n">
+      <c r="A185" s="5" t="n">
         <v>44517.95833333334</v>
       </c>
-      <c r="B185" s="3" t="n">
+      <c r="B185" s="5" t="n">
         <v>44518.25</v>
       </c>
       <c r="C185" s="2" t="n">
@@ -12030,10 +12413,10 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="3" t="n">
+      <c r="A186" s="5" t="n">
         <v>44518.41666666666</v>
       </c>
-      <c r="B186" s="3" t="n">
+      <c r="B186" s="5" t="n">
         <v>44518.91666666666</v>
       </c>
       <c r="C186" s="2" t="n">
@@ -12080,10 +12463,10 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="3" t="n">
+      <c r="A187" s="5" t="n">
         <v>44525.16666666666</v>
       </c>
-      <c r="B187" s="3" t="n">
+      <c r="B187" s="5" t="n">
         <v>44525.58333333334</v>
       </c>
       <c r="C187" s="2" t="n">
@@ -12130,10 +12513,10 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="3" t="n">
+      <c r="A188" s="5" t="n">
         <v>44530.79166666666</v>
       </c>
-      <c r="B188" s="3" t="n">
+      <c r="B188" s="5" t="n">
         <v>44531.625</v>
       </c>
       <c r="C188" s="2" t="n">
@@ -12180,10 +12563,10 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="3" t="n">
+      <c r="A189" s="5" t="n">
         <v>44543.45833333334</v>
       </c>
-      <c r="B189" s="3" t="n">
+      <c r="B189" s="5" t="n">
         <v>44543.58333333334</v>
       </c>
       <c r="C189" s="2" t="n">
@@ -12230,10 +12613,10 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="3" t="n">
+      <c r="A190" s="5" t="n">
         <v>44547.08333333334</v>
       </c>
-      <c r="B190" s="3" t="n">
+      <c r="B190" s="5" t="n">
         <v>44547.375</v>
       </c>
       <c r="C190" s="2" t="n">
@@ -12280,10 +12663,10 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="3" t="n">
+      <c r="A191" s="5" t="n">
         <v>44547.5</v>
       </c>
-      <c r="B191" s="3" t="n">
+      <c r="B191" s="5" t="n">
         <v>44548.20833333334</v>
       </c>
       <c r="C191" s="2" t="n">
@@ -12330,10 +12713,10 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="3" t="n">
+      <c r="A192" s="5" t="n">
         <v>44556.25</v>
       </c>
-      <c r="B192" s="3" t="n">
+      <c r="B192" s="5" t="n">
         <v>44556.625</v>
       </c>
       <c r="C192" s="2" t="n">
@@ -12380,10 +12763,10 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="3" t="n">
+      <c r="A193" s="5" t="n">
         <v>44556.79166666666</v>
       </c>
-      <c r="B193" s="3" t="n">
+      <c r="B193" s="5" t="n">
         <v>44557</v>
       </c>
       <c r="C193" s="2" t="n">
@@ -12430,10 +12813,10 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="3" t="n">
+      <c r="A194" s="5" t="n">
         <v>44563.875</v>
       </c>
-      <c r="B194" s="3" t="n">
+      <c r="B194" s="5" t="n">
         <v>44566.16666666666</v>
       </c>
       <c r="C194" s="2" t="n">
@@ -12480,10 +12863,10 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="3" t="n">
+      <c r="A195" s="5" t="n">
         <v>44568.66666666666</v>
       </c>
-      <c r="B195" s="3" t="n">
+      <c r="B195" s="5" t="n">
         <v>44570.375</v>
       </c>
       <c r="C195" s="2" t="n">
@@ -12530,10 +12913,10 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="3" t="n">
+      <c r="A196" s="5" t="n">
         <v>44573.33333333334</v>
       </c>
-      <c r="B196" s="3" t="n">
+      <c r="B196" s="5" t="n">
         <v>44573.875</v>
       </c>
       <c r="C196" s="2" t="n">
@@ -12580,10 +12963,10 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="3" t="n">
+      <c r="A197" s="5" t="n">
         <v>44579.125</v>
       </c>
-      <c r="B197" s="3" t="n">
+      <c r="B197" s="5" t="n">
         <v>44579.58333333334</v>
       </c>
       <c r="C197" s="2" t="n">
@@ -12630,10 +13013,10 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="3" t="n">
+      <c r="A198" s="5" t="n">
         <v>44579.95833333334</v>
       </c>
-      <c r="B198" s="3" t="n">
+      <c r="B198" s="5" t="n">
         <v>44582.125</v>
       </c>
       <c r="C198" s="2" t="n">
@@ -12680,10 +13063,10 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="3" t="n">
+      <c r="A199" s="5" t="n">
         <v>44582.29166666666</v>
       </c>
-      <c r="B199" s="3" t="n">
+      <c r="B199" s="5" t="n">
         <v>44582.91666666666</v>
       </c>
       <c r="C199" s="2" t="n">
@@ -12730,10 +13113,10 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="3" t="n">
+      <c r="A200" s="5" t="n">
         <v>44583.16666666666</v>
       </c>
-      <c r="B200" s="3" t="n">
+      <c r="B200" s="5" t="n">
         <v>44583.25</v>
       </c>
       <c r="C200" s="2" t="n">
@@ -12780,10 +13163,10 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="3" t="n">
+      <c r="A201" s="5" t="n">
         <v>44584.625</v>
       </c>
-      <c r="B201" s="3" t="n">
+      <c r="B201" s="5" t="n">
         <v>44585.04166666666</v>
       </c>
       <c r="C201" s="2" t="n">
@@ -12830,10 +13213,10 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="3" t="n">
+      <c r="A202" s="5" t="n">
         <v>44585.66666666666</v>
       </c>
-      <c r="B202" s="3" t="n">
+      <c r="B202" s="5" t="n">
         <v>44586</v>
       </c>
       <c r="C202" s="2" t="n">
@@ -12880,10 +13263,10 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="3" t="n">
+      <c r="A203" s="5" t="n">
         <v>44586.16666666666</v>
       </c>
-      <c r="B203" s="3" t="n">
+      <c r="B203" s="5" t="n">
         <v>44586.45833333334</v>
       </c>
       <c r="C203" s="2" t="n">
@@ -12930,10 +13313,10 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="3" t="n">
+      <c r="A204" s="5" t="n">
         <v>44598.41666666666</v>
       </c>
-      <c r="B204" s="3" t="n">
+      <c r="B204" s="5" t="n">
         <v>44599.375</v>
       </c>
       <c r="C204" s="2" t="n">
@@ -12980,10 +13363,10 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="3" t="n">
+      <c r="A205" s="5" t="n">
         <v>44600.875</v>
       </c>
-      <c r="B205" s="3" t="n">
+      <c r="B205" s="5" t="n">
         <v>44601.08333333334</v>
       </c>
       <c r="C205" s="2" t="n">
@@ -13030,10 +13413,10 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="3" t="n">
+      <c r="A206" s="5" t="n">
         <v>44601.20833333334</v>
       </c>
-      <c r="B206" s="3" t="n">
+      <c r="B206" s="5" t="n">
         <v>44601.5</v>
       </c>
       <c r="C206" s="2" t="n">
@@ -13080,10 +13463,10 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="3" t="n">
+      <c r="A207" s="5" t="n">
         <v>44601.83333333334</v>
       </c>
-      <c r="B207" s="3" t="n">
+      <c r="B207" s="5" t="n">
         <v>44602.20833333334</v>
       </c>
       <c r="C207" s="2" t="n">
@@ -13130,10 +13513,10 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="3" t="n">
+      <c r="A208" s="5" t="n">
         <v>44602.375</v>
       </c>
-      <c r="B208" s="3" t="n">
+      <c r="B208" s="5" t="n">
         <v>44602.58333333334</v>
       </c>
       <c r="C208" s="2" t="n">
@@ -13180,10 +13563,10 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="3" t="n">
+      <c r="A209" s="5" t="n">
         <v>44602.875</v>
       </c>
-      <c r="B209" s="3" t="n">
+      <c r="B209" s="5" t="n">
         <v>44602.95833333334</v>
       </c>
       <c r="C209" s="2" t="n">
@@ -13230,10 +13613,10 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="3" t="n">
+      <c r="A210" s="5" t="n">
         <v>44605.29166666666</v>
       </c>
-      <c r="B210" s="3" t="n">
+      <c r="B210" s="5" t="n">
         <v>44605.75</v>
       </c>
       <c r="C210" s="2" t="n">
@@ -13280,10 +13663,10 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="3" t="n">
+      <c r="A211" s="5" t="n">
         <v>44606.625</v>
       </c>
-      <c r="B211" s="3" t="n">
+      <c r="B211" s="5" t="n">
         <v>44606.75</v>
       </c>
       <c r="C211" s="2" t="n">
@@ -13330,10 +13713,10 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="3" t="n">
+      <c r="A212" s="5" t="n">
         <v>44607.79166666666</v>
       </c>
-      <c r="B212" s="3" t="n">
+      <c r="B212" s="5" t="n">
         <v>44608.04166666666</v>
       </c>
       <c r="C212" s="2" t="n">
@@ -13380,10 +13763,10 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="3" t="n">
+      <c r="A213" s="5" t="n">
         <v>44610.33333333334</v>
       </c>
-      <c r="B213" s="3" t="n">
+      <c r="B213" s="5" t="n">
         <v>44610.625</v>
       </c>
       <c r="C213" s="2" t="n">
@@ -13430,10 +13813,10 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="3" t="n">
+      <c r="A214" s="5" t="n">
         <v>44621.95833333334</v>
       </c>
-      <c r="B214" s="3" t="n">
+      <c r="B214" s="5" t="n">
         <v>44622.04166666666</v>
       </c>
       <c r="C214" s="2" t="n">
@@ -13480,10 +13863,10 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="3" t="n">
+      <c r="A215" s="5" t="n">
         <v>44622.16666666666</v>
       </c>
-      <c r="B215" s="3" t="n">
+      <c r="B215" s="5" t="n">
         <v>44622.45833333334</v>
       </c>
       <c r="C215" s="2" t="n">
@@ -13530,10 +13913,10 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="3" t="n">
+      <c r="A216" s="5" t="n">
         <v>44625.375</v>
       </c>
-      <c r="B216" s="3" t="n">
+      <c r="B216" s="5" t="n">
         <v>44627</v>
       </c>
       <c r="C216" s="2" t="n">
@@ -13580,10 +13963,10 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="3" t="n">
+      <c r="A217" s="5" t="n">
         <v>44628</v>
       </c>
-      <c r="B217" s="3" t="n">
+      <c r="B217" s="5" t="n">
         <v>44628.08333333334</v>
       </c>
       <c r="C217" s="2" t="n">
@@ -13630,10 +14013,10 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="3" t="n">
+      <c r="A218" s="5" t="n">
         <v>44628.625</v>
       </c>
-      <c r="B218" s="3" t="n">
+      <c r="B218" s="5" t="n">
         <v>44628.91666666666</v>
       </c>
       <c r="C218" s="2" t="n">
@@ -13680,10 +14063,10 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="3" t="n">
+      <c r="A219" s="5" t="n">
         <v>44630.16666666666</v>
       </c>
-      <c r="B219" s="3" t="n">
+      <c r="B219" s="5" t="n">
         <v>44630.875</v>
       </c>
       <c r="C219" s="2" t="n">
@@ -13730,10 +14113,10 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="3" t="n">
+      <c r="A220" s="5" t="n">
         <v>44633.5</v>
       </c>
-      <c r="B220" s="3" t="n">
+      <c r="B220" s="5" t="n">
         <v>44633.70833333334</v>
       </c>
       <c r="C220" s="2" t="n">
@@ -13780,10 +14163,10 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="3" t="n">
+      <c r="A221" s="5" t="n">
         <v>44638.70833333334</v>
       </c>
-      <c r="B221" s="3" t="n">
+      <c r="B221" s="5" t="n">
         <v>44639.08333333334</v>
       </c>
       <c r="C221" s="2" t="n">
@@ -13830,10 +14213,10 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="3" t="n">
+      <c r="A222" s="5" t="n">
         <v>44639.25</v>
       </c>
-      <c r="B222" s="3" t="n">
+      <c r="B222" s="5" t="n">
         <v>44639.45833333334</v>
       </c>
       <c r="C222" s="2" t="n">
@@ -13880,10 +14263,10 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="3" t="n">
+      <c r="A223" s="5" t="n">
         <v>44641.29166666666</v>
       </c>
-      <c r="B223" s="3" t="n">
+      <c r="B223" s="5" t="n">
         <v>44641.41666666666</v>
       </c>
       <c r="C223" s="2" t="n">
@@ -13930,10 +14313,10 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="3" t="n">
+      <c r="A224" s="5" t="n">
         <v>44645.33333333334</v>
       </c>
-      <c r="B224" s="3" t="n">
+      <c r="B224" s="5" t="n">
         <v>44645.66666666666</v>
       </c>
       <c r="C224" s="2" t="n">
@@ -13980,10 +14363,10 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="3" t="n">
+      <c r="A225" s="5" t="n">
         <v>44648.25</v>
       </c>
-      <c r="B225" s="3" t="n">
+      <c r="B225" s="5" t="n">
         <v>44648.91666666666</v>
       </c>
       <c r="C225" s="2" t="n">
@@ -14030,10 +14413,10 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="3" t="n">
+      <c r="A226" s="5" t="n">
         <v>44649.66666666666</v>
       </c>
-      <c r="B226" s="3" t="n">
+      <c r="B226" s="5" t="n">
         <v>44650.33333333334</v>
       </c>
       <c r="C226" s="2" t="n">
@@ -14080,10 +14463,10 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="3" t="n">
+      <c r="A227" s="5" t="n">
         <v>44650.5</v>
       </c>
-      <c r="B227" s="3" t="n">
+      <c r="B227" s="5" t="n">
         <v>44650.75</v>
       </c>
       <c r="C227" s="2" t="n">
@@ -14130,10 +14513,10 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="3" t="n">
+      <c r="A228" s="5" t="n">
         <v>44652.04166666666</v>
       </c>
-      <c r="B228" s="3" t="n">
+      <c r="B228" s="5" t="n">
         <v>44652.29166666666</v>
       </c>
       <c r="C228" s="2" t="n">
@@ -14180,10 +14563,10 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="3" t="n">
+      <c r="A229" s="5" t="n">
         <v>44659.08333333334</v>
       </c>
-      <c r="B229" s="3" t="n">
+      <c r="B229" s="5" t="n">
         <v>44659.41666666666</v>
       </c>
       <c r="C229" s="2" t="n">
@@ -14230,10 +14613,10 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="3" t="n">
+      <c r="A230" s="5" t="n">
         <v>44662.16666666666</v>
       </c>
-      <c r="B230" s="3" t="n">
+      <c r="B230" s="5" t="n">
         <v>44662.58333333334</v>
       </c>
       <c r="C230" s="2" t="n">
@@ -14280,10 +14663,10 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="3" t="n">
+      <c r="A231" s="5" t="n">
         <v>44662.70833333334</v>
       </c>
-      <c r="B231" s="3" t="n">
+      <c r="B231" s="5" t="n">
         <v>44662.79166666666</v>
       </c>
       <c r="C231" s="2" t="n">
@@ -14330,10 +14713,10 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="3" t="n">
+      <c r="A232" s="5" t="n">
         <v>44669.66666666666</v>
       </c>
-      <c r="B232" s="3" t="n">
+      <c r="B232" s="5" t="n">
         <v>44669.875</v>
       </c>
       <c r="C232" s="2" t="n">
@@ -14380,10 +14763,10 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="3" t="n">
+      <c r="A233" s="5" t="n">
         <v>44671.5</v>
       </c>
-      <c r="B233" s="3" t="n">
+      <c r="B233" s="5" t="n">
         <v>44671.95833333334</v>
       </c>
       <c r="C233" s="2" t="n">
@@ -14430,10 +14813,10 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="3" t="n">
+      <c r="A234" s="5" t="n">
         <v>44672.66666666666</v>
       </c>
-      <c r="B234" s="3" t="n">
+      <c r="B234" s="5" t="n">
         <v>44673.20833333334</v>
       </c>
       <c r="C234" s="2" t="n">
@@ -14480,10 +14863,10 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="3" t="n">
+      <c r="A235" s="5" t="n">
         <v>44674.5</v>
       </c>
-      <c r="B235" s="3" t="n">
+      <c r="B235" s="5" t="n">
         <v>44674.95833333334</v>
       </c>
       <c r="C235" s="2" t="n">
@@ -14530,10 +14913,10 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="3" t="n">
+      <c r="A236" s="5" t="n">
         <v>44680.54166666666</v>
       </c>
-      <c r="B236" s="3" t="n">
+      <c r="B236" s="5" t="n">
         <v>44681.29166666666</v>
       </c>
       <c r="C236" s="2" t="n">
@@ -14580,10 +14963,10 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="3" t="n">
+      <c r="A237" s="5" t="n">
         <v>44682.29166666666</v>
       </c>
-      <c r="B237" s="3" t="n">
+      <c r="B237" s="5" t="n">
         <v>44682.66666666666</v>
       </c>
       <c r="C237" s="2" t="n">
@@ -14630,10 +15013,10 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="3" t="n">
+      <c r="A238" s="5" t="n">
         <v>44687.45833333334</v>
       </c>
-      <c r="B238" s="3" t="n">
+      <c r="B238" s="5" t="n">
         <v>44687.58333333334</v>
       </c>
       <c r="C238" s="2" t="n">
@@ -14680,10 +15063,10 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="3" t="n">
+      <c r="A239" s="5" t="n">
         <v>44687.70833333334</v>
       </c>
-      <c r="B239" s="3" t="n">
+      <c r="B239" s="5" t="n">
         <v>44688.20833333334</v>
       </c>
       <c r="C239" s="2" t="n">
@@ -14730,10 +15113,10 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="3" t="n">
+      <c r="A240" s="5" t="n">
         <v>44688.33333333334</v>
       </c>
-      <c r="B240" s="3" t="n">
+      <c r="B240" s="5" t="n">
         <v>44688.79166666666</v>
       </c>
       <c r="C240" s="2" t="n">
@@ -14780,10 +15163,10 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="3" t="n">
+      <c r="A241" s="5" t="n">
         <v>44689.83333333334</v>
       </c>
-      <c r="B241" s="3" t="n">
+      <c r="B241" s="5" t="n">
         <v>44690.16666666666</v>
       </c>
       <c r="C241" s="2" t="n">
@@ -14830,10 +15213,10 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="3" t="n">
+      <c r="A242" s="5" t="n">
         <v>44690.83333333334</v>
       </c>
-      <c r="B242" s="3" t="n">
+      <c r="B242" s="5" t="n">
         <v>44690.91666666666</v>
       </c>
       <c r="C242" s="2" t="n">
@@ -14880,10 +15263,10 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="3" t="n">
+      <c r="A243" s="5" t="n">
         <v>44692.75</v>
       </c>
-      <c r="B243" s="3" t="n">
+      <c r="B243" s="5" t="n">
         <v>44692.875</v>
       </c>
       <c r="C243" s="2" t="n">
@@ -14930,10 +15313,10 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="3" t="n">
+      <c r="A244" s="5" t="n">
         <v>44694.45833333334</v>
       </c>
-      <c r="B244" s="3" t="n">
+      <c r="B244" s="5" t="n">
         <v>44694.54166666666</v>
       </c>
       <c r="C244" s="2" t="n">
@@ -14980,10 +15363,10 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="3" t="n">
+      <c r="A245" s="5" t="n">
         <v>44696</v>
       </c>
-      <c r="B245" s="3" t="n">
+      <c r="B245" s="5" t="n">
         <v>44696.16666666666</v>
       </c>
       <c r="C245" s="2" t="n">
@@ -15030,10 +15413,10 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="3" t="n">
+      <c r="A246" s="5" t="n">
         <v>44697.75</v>
       </c>
-      <c r="B246" s="3" t="n">
+      <c r="B246" s="5" t="n">
         <v>44698.83333333334</v>
       </c>
       <c r="C246" s="2" t="n">
@@ -15080,10 +15463,10 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="3" t="n">
+      <c r="A247" s="5" t="n">
         <v>44699</v>
       </c>
-      <c r="B247" s="3" t="n">
+      <c r="B247" s="5" t="n">
         <v>44700.75</v>
       </c>
       <c r="C247" s="2" t="n">
@@ -15130,10 +15513,10 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="3" t="n">
+      <c r="A248" s="5" t="n">
         <v>44701.25</v>
       </c>
-      <c r="B248" s="3" t="n">
+      <c r="B248" s="5" t="n">
         <v>44701.66666666666</v>
       </c>
       <c r="C248" s="2" t="n">
@@ -15180,10 +15563,10 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="3" t="n">
+      <c r="A249" s="5" t="n">
         <v>44702.41666666666</v>
       </c>
-      <c r="B249" s="3" t="n">
+      <c r="B249" s="5" t="n">
         <v>44704.95833333334</v>
       </c>
       <c r="C249" s="2" t="n">
@@ -15230,10 +15613,10 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="3" t="n">
+      <c r="A250" s="5" t="n">
         <v>44705.16666666666</v>
       </c>
-      <c r="B250" s="3" t="n">
+      <c r="B250" s="5" t="n">
         <v>44707.875</v>
       </c>
       <c r="C250" s="2" t="n">
@@ -15280,10 +15663,10 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="3" t="n">
+      <c r="A251" s="5" t="n">
         <v>44708.29166666666</v>
       </c>
-      <c r="B251" s="3" t="n">
+      <c r="B251" s="5" t="n">
         <v>44708.58333333334</v>
       </c>
       <c r="C251" s="2" t="n">
@@ -15330,10 +15713,10 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="3" t="n">
+      <c r="A252" s="5" t="n">
         <v>44714.375</v>
       </c>
-      <c r="B252" s="3" t="n">
+      <c r="B252" s="5" t="n">
         <v>44714.875</v>
       </c>
       <c r="C252" s="2" t="n">
@@ -15380,10 +15763,10 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="3" t="n">
+      <c r="A253" s="5" t="n">
         <v>44715</v>
       </c>
-      <c r="B253" s="3" t="n">
+      <c r="B253" s="5" t="n">
         <v>44717.08333333334</v>
       </c>
       <c r="C253" s="2" t="n">
@@ -15430,10 +15813,10 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="3" t="n">
+      <c r="A254" s="5" t="n">
         <v>44717.20833333334</v>
       </c>
-      <c r="B254" s="3" t="n">
+      <c r="B254" s="5" t="n">
         <v>44718.375</v>
       </c>
       <c r="C254" s="2" t="n">
@@ -15480,10 +15863,10 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="3" t="n">
+      <c r="A255" s="5" t="n">
         <v>44718.5</v>
       </c>
-      <c r="B255" s="3" t="n">
+      <c r="B255" s="5" t="n">
         <v>44718.58333333334</v>
       </c>
       <c r="C255" s="2" t="n">
@@ -15530,10 +15913,10 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="3" t="n">
+      <c r="A256" s="5" t="n">
         <v>44719.16666666666</v>
       </c>
-      <c r="B256" s="3" t="n">
+      <c r="B256" s="5" t="n">
         <v>44720.45833333334</v>
       </c>
       <c r="C256" s="2" t="n">
@@ -15580,10 +15963,10 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="3" t="n">
+      <c r="A257" s="5" t="n">
         <v>44723.20833333334</v>
       </c>
-      <c r="B257" s="3" t="n">
+      <c r="B257" s="5" t="n">
         <v>44723.91666666666</v>
       </c>
       <c r="C257" s="2" t="n">
@@ -15630,10 +16013,10 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="3" t="n">
+      <c r="A258" s="5" t="n">
         <v>44727.20833333334</v>
       </c>
-      <c r="B258" s="3" t="n">
+      <c r="B258" s="5" t="n">
         <v>44728</v>
       </c>
       <c r="C258" s="2" t="n">
@@ -15680,10 +16063,10 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="3" t="n">
+      <c r="A259" s="5" t="n">
         <v>44728.125</v>
       </c>
-      <c r="B259" s="3" t="n">
+      <c r="B259" s="5" t="n">
         <v>44728.875</v>
       </c>
       <c r="C259" s="2" t="n">
@@ -15730,10 +16113,10 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="3" t="n">
+      <c r="A260" s="5" t="n">
         <v>44729</v>
       </c>
-      <c r="B260" s="3" t="n">
+      <c r="B260" s="5" t="n">
         <v>44729.5</v>
       </c>
       <c r="C260" s="2" t="n">
@@ -15780,10 +16163,10 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="3" t="n">
+      <c r="A261" s="5" t="n">
         <v>44729.625</v>
       </c>
-      <c r="B261" s="3" t="n">
+      <c r="B261" s="5" t="n">
         <v>44729.83333333334</v>
       </c>
       <c r="C261" s="2" t="n">
@@ -15830,10 +16213,10 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="3" t="n">
+      <c r="A262" s="5" t="n">
         <v>44731.29166666666</v>
       </c>
-      <c r="B262" s="3" t="n">
+      <c r="B262" s="5" t="n">
         <v>44731.75</v>
       </c>
       <c r="C262" s="2" t="n">
@@ -15880,10 +16263,10 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="3" t="n">
+      <c r="A263" s="5" t="n">
         <v>44732.25</v>
       </c>
-      <c r="B263" s="3" t="n">
+      <c r="B263" s="5" t="n">
         <v>44732.5</v>
       </c>
       <c r="C263" s="2" t="n">
@@ -15930,10 +16313,10 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="3" t="n">
+      <c r="A264" s="5" t="n">
         <v>44732.70833333334</v>
       </c>
-      <c r="B264" s="3" t="n">
+      <c r="B264" s="5" t="n">
         <v>44732.83333333334</v>
       </c>
       <c r="C264" s="2" t="n">
@@ -15980,10 +16363,10 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="3" t="n">
+      <c r="A265" s="5" t="n">
         <v>44732.95833333334</v>
       </c>
-      <c r="B265" s="3" t="n">
+      <c r="B265" s="5" t="n">
         <v>44734.5</v>
       </c>
       <c r="C265" s="2" t="n">
@@ -16030,10 +16413,10 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="3" t="n">
+      <c r="A266" s="5" t="n">
         <v>44734.625</v>
       </c>
-      <c r="B266" s="3" t="n">
+      <c r="B266" s="5" t="n">
         <v>44735.41666666666</v>
       </c>
       <c r="C266" s="2" t="n">
@@ -16080,10 +16463,10 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="3" t="n">
+      <c r="A267" s="5" t="n">
         <v>44736.375</v>
       </c>
-      <c r="B267" s="3" t="n">
+      <c r="B267" s="5" t="n">
         <v>44736.66666666666</v>
       </c>
       <c r="C267" s="2" t="n">
@@ -16130,10 +16513,10 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="3" t="n">
+      <c r="A268" s="5" t="n">
         <v>44736.83333333334</v>
       </c>
-      <c r="B268" s="3" t="n">
+      <c r="B268" s="5" t="n">
         <v>44737</v>
       </c>
       <c r="C268" s="2" t="n">
@@ -16180,10 +16563,10 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="3" t="n">
+      <c r="A269" s="5" t="n">
         <v>44750.41666666666</v>
       </c>
-      <c r="B269" s="3" t="n">
+      <c r="B269" s="5" t="n">
         <v>44750.70833333334</v>
       </c>
       <c r="C269" s="2" t="n">
@@ -16230,10 +16613,10 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="3" t="n">
+      <c r="A270" s="5" t="n">
         <v>44752.66666666666</v>
       </c>
-      <c r="B270" s="3" t="n">
+      <c r="B270" s="5" t="n">
         <v>44752.75</v>
       </c>
       <c r="C270" s="2" t="n">
@@ -16280,10 +16663,10 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="3" t="n">
+      <c r="A271" s="5" t="n">
         <v>44752.95833333334</v>
       </c>
-      <c r="B271" s="3" t="n">
+      <c r="B271" s="5" t="n">
         <v>44753.25</v>
       </c>
       <c r="C271" s="2" t="n">
@@ -16330,10 +16713,10 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="3" t="n">
+      <c r="A272" s="5" t="n">
         <v>44755.95833333334</v>
       </c>
-      <c r="B272" s="3" t="n">
+      <c r="B272" s="5" t="n">
         <v>44756.375</v>
       </c>
       <c r="C272" s="2" t="n">
@@ -16380,10 +16763,10 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="3" t="n">
+      <c r="A273" s="5" t="n">
         <v>44774.375</v>
       </c>
-      <c r="B273" s="3" t="n">
+      <c r="B273" s="5" t="n">
         <v>44774.58333333334</v>
       </c>
       <c r="C273" s="2" t="n">
@@ -16430,10 +16813,10 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="3" t="n">
+      <c r="A274" s="5" t="n">
         <v>44781.33333333334</v>
       </c>
-      <c r="B274" s="3" t="n">
+      <c r="B274" s="5" t="n">
         <v>44781.625</v>
       </c>
       <c r="C274" s="2" t="n">
@@ -16480,10 +16863,10 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="3" t="n">
+      <c r="A275" s="5" t="n">
         <v>44781.95833333334</v>
       </c>
-      <c r="B275" s="3" t="n">
+      <c r="B275" s="5" t="n">
         <v>44782.25</v>
       </c>
       <c r="C275" s="2" t="n">
@@ -16530,10 +16913,10 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="3" t="n">
+      <c r="A276" s="5" t="n">
         <v>44796.70833333334</v>
       </c>
-      <c r="B276" s="3" t="n">
+      <c r="B276" s="5" t="n">
         <v>44796.91666666666</v>
       </c>
       <c r="C276" s="2" t="n">
@@ -16580,10 +16963,10 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="3" t="n">
+      <c r="A277" s="5" t="n">
         <v>44810.66666666666</v>
       </c>
-      <c r="B277" s="3" t="n">
+      <c r="B277" s="5" t="n">
         <v>44810.95833333334</v>
       </c>
       <c r="C277" s="2" t="n">
@@ -16630,10 +17013,10 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="3" t="n">
+      <c r="A278" s="5" t="n">
         <v>44820.66666666666</v>
       </c>
-      <c r="B278" s="3" t="n">
+      <c r="B278" s="5" t="n">
         <v>44820.83333333334</v>
       </c>
       <c r="C278" s="2" t="n">
@@ -16680,10 +17063,10 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="3" t="n">
+      <c r="A279" s="5" t="n">
         <v>44827.29166666666</v>
       </c>
-      <c r="B279" s="3" t="n">
+      <c r="B279" s="5" t="n">
         <v>44827.625</v>
       </c>
       <c r="C279" s="2" t="n">
@@ -16730,10 +17113,10 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="3" t="n">
+      <c r="A280" s="5" t="n">
         <v>44839.04166666666</v>
       </c>
-      <c r="B280" s="3" t="n">
+      <c r="B280" s="5" t="n">
         <v>44839.29166666666</v>
       </c>
       <c r="C280" s="2" t="n">
@@ -16780,10 +17163,10 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="3" t="n">
+      <c r="A281" s="5" t="n">
         <v>44848.75</v>
       </c>
-      <c r="B281" s="3" t="n">
+      <c r="B281" s="5" t="n">
         <v>44849.20833333334</v>
       </c>
       <c r="C281" s="2" t="n">
@@ -16830,10 +17213,10 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="3" t="n">
+      <c r="A282" s="5" t="n">
         <v>44852.45833333334</v>
       </c>
-      <c r="B282" s="3" t="n">
+      <c r="B282" s="5" t="n">
         <v>44852.79166666666</v>
       </c>
       <c r="C282" s="2" t="n">
@@ -16880,10 +17263,10 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="3" t="n">
+      <c r="A283" s="5" t="n">
         <v>44866.41666666666</v>
       </c>
-      <c r="B283" s="3" t="n">
+      <c r="B283" s="5" t="n">
         <v>44866.5</v>
       </c>
       <c r="C283" s="2" t="n">
@@ -16930,10 +17313,10 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="3" t="n">
+      <c r="A284" s="5" t="n">
         <v>44867.45833333334</v>
       </c>
-      <c r="B284" s="3" t="n">
+      <c r="B284" s="5" t="n">
         <v>44867.58333333334</v>
       </c>
       <c r="C284" s="2" t="n">
@@ -16980,10 +17363,10 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="3" t="n">
+      <c r="A285" s="5" t="n">
         <v>44869.79166666666</v>
       </c>
-      <c r="B285" s="3" t="n">
+      <c r="B285" s="5" t="n">
         <v>44869.95833333334</v>
       </c>
       <c r="C285" s="2" t="n">
@@ -17030,10 +17413,10 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="3" t="n">
+      <c r="A286" s="5" t="n">
         <v>44870.66666666666</v>
       </c>
-      <c r="B286" s="3" t="n">
+      <c r="B286" s="5" t="n">
         <v>44870.91666666666</v>
       </c>
       <c r="C286" s="2" t="n">
@@ -17080,10 +17463,10 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="3" t="n">
+      <c r="A287" s="5" t="n">
         <v>44922.33333333334</v>
       </c>
-      <c r="B287" s="3" t="n">
+      <c r="B287" s="5" t="n">
         <v>44922.79166666666</v>
       </c>
       <c r="C287" s="2" t="n">
@@ -17130,10 +17513,10 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="3" t="n">
+      <c r="A288" s="5" t="n">
         <v>44934.83333333334</v>
       </c>
-      <c r="B288" s="3" t="n">
+      <c r="B288" s="5" t="n">
         <v>44935.5</v>
       </c>
       <c r="C288" s="2" t="n">
@@ -17180,10 +17563,10 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="3" t="n">
+      <c r="A289" s="5" t="n">
         <v>44962</v>
       </c>
-      <c r="B289" s="3" t="n">
+      <c r="B289" s="5" t="n">
         <v>44962.54166666666</v>
       </c>
       <c r="C289" s="2" t="n">
@@ -17230,10 +17613,10 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="3" t="n">
+      <c r="A290" s="5" t="n">
         <v>44968.95833333334</v>
       </c>
-      <c r="B290" s="3" t="n">
+      <c r="B290" s="5" t="n">
         <v>44969.16666666666</v>
       </c>
       <c r="C290" s="2" t="n">
@@ -17280,10 +17663,10 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="3" t="n">
+      <c r="A291" s="5" t="n">
         <v>44972.70833333334</v>
       </c>
-      <c r="B291" s="3" t="n">
+      <c r="B291" s="5" t="n">
         <v>44973.04166666666</v>
       </c>
       <c r="C291" s="2" t="n">
@@ -17330,10 +17713,10 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="3" t="n">
+      <c r="A292" s="5" t="n">
         <v>44987.33333333334</v>
       </c>
-      <c r="B292" s="3" t="n">
+      <c r="B292" s="5" t="n">
         <v>44987.5</v>
       </c>
       <c r="C292" s="2" t="n">
@@ -17380,10 +17763,10 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="3" t="n">
+      <c r="A293" s="5" t="n">
         <v>45002.375</v>
       </c>
-      <c r="B293" s="3" t="n">
+      <c r="B293" s="5" t="n">
         <v>45002.91666666666</v>
       </c>
       <c r="C293" s="2" t="n">
@@ -17430,10 +17813,10 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="3" t="n">
+      <c r="A294" s="5" t="n">
         <v>45043.75</v>
       </c>
-      <c r="B294" s="3" t="n">
+      <c r="B294" s="5" t="n">
         <v>45043.95833333334</v>
       </c>
       <c r="C294" s="2" t="n">
@@ -17480,10 +17863,10 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="3" t="n">
+      <c r="A295" s="5" t="n">
         <v>45044.125</v>
       </c>
-      <c r="B295" s="3" t="n">
+      <c r="B295" s="5" t="n">
         <v>45044.29166666666</v>
       </c>
       <c r="C295" s="2" t="n">
@@ -17530,10 +17913,10 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="3" t="n">
+      <c r="A296" s="5" t="n">
         <v>45054.625</v>
       </c>
-      <c r="B296" s="3" t="n">
+      <c r="B296" s="5" t="n">
         <v>45054.875</v>
       </c>
       <c r="C296" s="2" t="n">
@@ -17580,10 +17963,10 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="3" t="n">
+      <c r="A297" s="5" t="n">
         <v>45066.58333333334</v>
       </c>
-      <c r="B297" s="3" t="n">
+      <c r="B297" s="5" t="n">
         <v>45067.125</v>
       </c>
       <c r="C297" s="2" t="n">
@@ -17630,10 +18013,10 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="3" t="n">
+      <c r="A298" s="5" t="n">
         <v>45068.54166666666</v>
       </c>
-      <c r="B298" s="3" t="n">
+      <c r="B298" s="5" t="n">
         <v>45069.08333333334</v>
       </c>
       <c r="C298" s="2" t="n">
@@ -17680,10 +18063,10 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="3" t="n">
+      <c r="A299" s="5" t="n">
         <v>45074.45833333334</v>
       </c>
-      <c r="B299" s="3" t="n">
+      <c r="B299" s="5" t="n">
         <v>45074.58333333334</v>
       </c>
       <c r="C299" s="2" t="n">
@@ -17730,10 +18113,10 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="3" t="n">
+      <c r="A300" s="5" t="n">
         <v>45075.625</v>
       </c>
-      <c r="B300" s="3" t="n">
+      <c r="B300" s="5" t="n">
         <v>45077.20833333334</v>
       </c>
       <c r="C300" s="2" t="n">
@@ -17780,10 +18163,10 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="3" t="n">
+      <c r="A301" s="5" t="n">
         <v>45078.66666666666</v>
       </c>
-      <c r="B301" s="3" t="n">
+      <c r="B301" s="5" t="n">
         <v>45079.16666666666</v>
       </c>
       <c r="C301" s="2" t="n">
@@ -17830,10 +18213,10 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="3" t="n">
+      <c r="A302" s="5" t="n">
         <v>45084.75</v>
       </c>
-      <c r="B302" s="3" t="n">
+      <c r="B302" s="5" t="n">
         <v>45085.125</v>
       </c>
       <c r="C302" s="2" t="n">
@@ -17880,10 +18263,10 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="3" t="n">
+      <c r="A303" s="5" t="n">
         <v>45093.45833333334</v>
       </c>
-      <c r="B303" s="3" t="n">
+      <c r="B303" s="5" t="n">
         <v>45093.95833333334</v>
       </c>
       <c r="C303" s="2" t="n">
@@ -17930,10 +18313,10 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="3" t="n">
+      <c r="A304" s="5" t="n">
         <v>45096.41666666666</v>
       </c>
-      <c r="B304" s="3" t="n">
+      <c r="B304" s="5" t="n">
         <v>45097.20833333334</v>
       </c>
       <c r="C304" s="2" t="n">
@@ -17980,10 +18363,10 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="3" t="n">
+      <c r="A305" s="5" t="n">
         <v>45097.33333333334</v>
       </c>
-      <c r="B305" s="3" t="n">
+      <c r="B305" s="5" t="n">
         <v>45097.5</v>
       </c>
       <c r="C305" s="2" t="n">
@@ -18030,10 +18413,10 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="3" t="n">
+      <c r="A306" s="5" t="n">
         <v>45098.45833333334</v>
       </c>
-      <c r="B306" s="3" t="n">
+      <c r="B306" s="5" t="n">
         <v>45100.41666666666</v>
       </c>
       <c r="C306" s="2" t="n">
@@ -18080,10 +18463,10 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="3" t="n">
+      <c r="A307" s="5" t="n">
         <v>45100.54166666666</v>
       </c>
-      <c r="B307" s="3" t="n">
+      <c r="B307" s="5" t="n">
         <v>45103.875</v>
       </c>
       <c r="C307" s="2" t="n">
@@ -18130,10 +18513,10 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="3" t="n">
+      <c r="A308" s="5" t="n">
         <v>45128.54166666666</v>
       </c>
-      <c r="B308" s="3" t="n">
+      <c r="B308" s="5" t="n">
         <v>45128.95833333334</v>
       </c>
       <c r="C308" s="2" t="n">
@@ -18180,10 +18563,10 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="3" t="n">
+      <c r="A309" s="5" t="n">
         <v>45130.25</v>
       </c>
-      <c r="B309" s="3" t="n">
+      <c r="B309" s="5" t="n">
         <v>45130.75</v>
       </c>
       <c r="C309" s="2" t="n">
@@ -18230,10 +18613,10 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="3" t="n">
+      <c r="A310" s="5" t="n">
         <v>45136.29166666666</v>
       </c>
-      <c r="B310" s="3" t="n">
+      <c r="B310" s="5" t="n">
         <v>45136.91666666666</v>
       </c>
       <c r="C310" s="2" t="n">
@@ -18280,10 +18663,10 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="3" t="n">
+      <c r="A311" s="5" t="n">
         <v>45137.29166666666</v>
       </c>
-      <c r="B311" s="3" t="n">
+      <c r="B311" s="5" t="n">
         <v>45138</v>
       </c>
       <c r="C311" s="2" t="n">
@@ -18330,10 +18713,10 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="3" t="n">
+      <c r="A312" s="5" t="n">
         <v>45139.33333333334</v>
       </c>
-      <c r="B312" s="3" t="n">
+      <c r="B312" s="5" t="n">
         <v>45139.83333333334</v>
       </c>
       <c r="C312" s="2" t="n">
@@ -18380,10 +18763,10 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="3" t="n">
+      <c r="A313" s="5" t="n">
         <v>45141.41666666666</v>
       </c>
-      <c r="B313" s="3" t="n">
+      <c r="B313" s="5" t="n">
         <v>45142</v>
       </c>
       <c r="C313" s="2" t="n">
@@ -18430,10 +18813,10 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="3" t="n">
+      <c r="A314" s="5" t="n">
         <v>45142.20833333334</v>
       </c>
-      <c r="B314" s="3" t="n">
+      <c r="B314" s="5" t="n">
         <v>45142.41666666666</v>
       </c>
       <c r="C314" s="2" t="n">
@@ -18480,10 +18863,10 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="3" t="n">
+      <c r="A315" s="5" t="n">
         <v>45146.75</v>
       </c>
-      <c r="B315" s="3" t="n">
+      <c r="B315" s="5" t="n">
         <v>45147.66666666666</v>
       </c>
       <c r="C315" s="2" t="n">
@@ -18530,10 +18913,10 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="3" t="n">
+      <c r="A316" s="5" t="n">
         <v>45148.16666666666</v>
       </c>
-      <c r="B316" s="3" t="n">
+      <c r="B316" s="5" t="n">
         <v>45148.29166666666</v>
       </c>
       <c r="C316" s="2" t="n">
@@ -18580,10 +18963,10 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="3" t="n">
+      <c r="A317" s="5" t="n">
         <v>45149.41666666666</v>
       </c>
-      <c r="B317" s="3" t="n">
+      <c r="B317" s="5" t="n">
         <v>45149.625</v>
       </c>
       <c r="C317" s="2" t="n">
@@ -18630,10 +19013,10 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="3" t="n">
+      <c r="A318" s="5" t="n">
         <v>45149.95833333334</v>
       </c>
-      <c r="B318" s="3" t="n">
+      <c r="B318" s="5" t="n">
         <v>45150.04166666666</v>
       </c>
       <c r="C318" s="2" t="n">
@@ -18680,10 +19063,10 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="3" t="n">
+      <c r="A319" s="5" t="n">
         <v>45150.375</v>
       </c>
-      <c r="B319" s="3" t="n">
+      <c r="B319" s="5" t="n">
         <v>45150.5</v>
       </c>
       <c r="C319" s="2" t="n">
@@ -18730,10 +19113,10 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="3" t="n">
+      <c r="A320" s="5" t="n">
         <v>45150.79166666666</v>
       </c>
-      <c r="B320" s="3" t="n">
+      <c r="B320" s="5" t="n">
         <v>45150.95833333334</v>
       </c>
       <c r="C320" s="2" t="n">
@@ -18780,10 +19163,10 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="3" t="n">
+      <c r="A321" s="5" t="n">
         <v>45151.91666666666</v>
       </c>
-      <c r="B321" s="3" t="n">
+      <c r="B321" s="5" t="n">
         <v>45152.25</v>
       </c>
       <c r="C321" s="2" t="n">
@@ -18830,10 +19213,10 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="3" t="n">
+      <c r="A322" s="5" t="n">
         <v>45152.41666666666</v>
       </c>
-      <c r="B322" s="3" t="n">
+      <c r="B322" s="5" t="n">
         <v>45152.58333333334</v>
       </c>
       <c r="C322" s="2" t="n">
@@ -18880,10 +19263,10 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="3" t="n">
+      <c r="A323" s="5" t="n">
         <v>45152.83333333334</v>
       </c>
-      <c r="B323" s="3" t="n">
+      <c r="B323" s="5" t="n">
         <v>45153</v>
       </c>
       <c r="C323" s="2" t="n">
@@ -18930,10 +19313,10 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="3" t="n">
+      <c r="A324" s="5" t="n">
         <v>45155.08333333334</v>
       </c>
-      <c r="B324" s="3" t="n">
+      <c r="B324" s="5" t="n">
         <v>45155.625</v>
       </c>
       <c r="C324" s="2" t="n">
@@ -18980,10 +19363,10 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="3" t="n">
+      <c r="A325" s="5" t="n">
         <v>45156.79166666666</v>
       </c>
-      <c r="B325" s="3" t="n">
+      <c r="B325" s="5" t="n">
         <v>45157.08333333334</v>
       </c>
       <c r="C325" s="2" t="n">
@@ -19030,10 +19413,10 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="3" t="n">
+      <c r="A326" s="5" t="n">
         <v>45158.625</v>
       </c>
-      <c r="B326" s="3" t="n">
+      <c r="B326" s="5" t="n">
         <v>45158.875</v>
       </c>
       <c r="C326" s="2" t="n">
@@ -19080,10 +19463,10 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="3" t="n">
+      <c r="A327" s="5" t="n">
         <v>45159.375</v>
       </c>
-      <c r="B327" s="3" t="n">
+      <c r="B327" s="5" t="n">
         <v>45160</v>
       </c>
       <c r="C327" s="2" t="n">
@@ -19130,10 +19513,10 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="3" t="n">
+      <c r="A328" s="5" t="n">
         <v>45166.45833333334</v>
       </c>
-      <c r="B328" s="3" t="n">
+      <c r="B328" s="5" t="n">
         <v>45166.875</v>
       </c>
       <c r="C328" s="2" t="n">
@@ -19180,10 +19563,10 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="3" t="n">
+      <c r="A329" s="5" t="n">
         <v>45167.79166666666</v>
       </c>
-      <c r="B329" s="3" t="n">
+      <c r="B329" s="5" t="n">
         <v>45167.875</v>
       </c>
       <c r="C329" s="2" t="n">
@@ -19230,10 +19613,10 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="3" t="n">
+      <c r="A330" s="5" t="n">
         <v>45168.25</v>
       </c>
-      <c r="B330" s="3" t="n">
+      <c r="B330" s="5" t="n">
         <v>45168.91666666666</v>
       </c>
       <c r="C330" s="2" t="n">
@@ -19280,10 +19663,10 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="3" t="n">
+      <c r="A331" s="5" t="n">
         <v>45169.83333333334</v>
       </c>
-      <c r="B331" s="3" t="n">
+      <c r="B331" s="5" t="n">
         <v>45170.45833333334</v>
       </c>
       <c r="C331" s="2" t="n">
@@ -19330,10 +19713,10 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="3" t="n">
+      <c r="A332" s="5" t="n">
         <v>45170.70833333334</v>
       </c>
-      <c r="B332" s="3" t="n">
+      <c r="B332" s="5" t="n">
         <v>45179.66666666666</v>
       </c>
       <c r="C332" s="2" t="n">
@@ -19380,10 +19763,10 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="3" t="n">
+      <c r="A333" s="5" t="n">
         <v>45180.5</v>
       </c>
-      <c r="B333" s="3" t="n">
+      <c r="B333" s="5" t="n">
         <v>45180.875</v>
       </c>
       <c r="C333" s="2" t="n">
@@ -19430,10 +19813,10 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="3" t="n">
+      <c r="A334" s="5" t="n">
         <v>45183.29166666666</v>
       </c>
-      <c r="B334" s="3" t="n">
+      <c r="B334" s="5" t="n">
         <v>45183.375</v>
       </c>
       <c r="C334" s="2" t="n">
@@ -19480,10 +19863,10 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="3" t="n">
+      <c r="A335" s="5" t="n">
         <v>45183.875</v>
       </c>
-      <c r="B335" s="3" t="n">
+      <c r="B335" s="5" t="n">
         <v>45184.20833333334</v>
       </c>
       <c r="C335" s="2" t="n">
@@ -19530,10 +19913,10 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="3" t="n">
+      <c r="A336" s="5" t="n">
         <v>45193.91666666666</v>
       </c>
-      <c r="B336" s="3" t="n">
+      <c r="B336" s="5" t="n">
         <v>45194</v>
       </c>
       <c r="C336" s="2" t="n">
@@ -19580,10 +19963,10 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="3" t="n">
+      <c r="A337" s="5" t="n">
         <v>45195.5</v>
       </c>
-      <c r="B337" s="3" t="n">
+      <c r="B337" s="5" t="n">
         <v>45196.08333333334</v>
       </c>
       <c r="C337" s="2" t="n">
@@ -19630,10 +20013,10 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="3" t="n">
+      <c r="A338" s="5" t="n">
         <v>45196.29166666666</v>
       </c>
-      <c r="B338" s="3" t="n">
+      <c r="B338" s="5" t="n">
         <v>45196.625</v>
       </c>
       <c r="C338" s="2" t="n">
@@ -19680,10 +20063,10 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="3" t="n">
+      <c r="A339" s="5" t="n">
         <v>45196.875</v>
       </c>
-      <c r="B339" s="3" t="n">
+      <c r="B339" s="5" t="n">
         <v>45197.04166666666</v>
       </c>
       <c r="C339" s="2" t="n">
@@ -19730,10 +20113,10 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="3" t="n">
+      <c r="A340" s="5" t="n">
         <v>45212.75</v>
       </c>
-      <c r="B340" s="3" t="n">
+      <c r="B340" s="5" t="n">
         <v>45213</v>
       </c>
       <c r="C340" s="2" t="n">
@@ -19780,10 +20163,10 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="3" t="n">
+      <c r="A341" s="5" t="n">
         <v>45231.375</v>
       </c>
-      <c r="B341" s="3" t="n">
+      <c r="B341" s="5" t="n">
         <v>45231.45833333334</v>
       </c>
       <c r="C341" s="2" t="n">
@@ -19830,10 +20213,10 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="3" t="n">
+      <c r="A342" s="5" t="n">
         <v>45234.95833333334</v>
       </c>
-      <c r="B342" s="3" t="n">
+      <c r="B342" s="5" t="n">
         <v>45235.20833333334</v>
       </c>
       <c r="C342" s="2" t="n">
@@ -19880,10 +20263,10 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="3" t="n">
+      <c r="A343" s="5" t="n">
         <v>45241.33333333334</v>
       </c>
-      <c r="B343" s="3" t="n">
+      <c r="B343" s="5" t="n">
         <v>45241.79166666666</v>
       </c>
       <c r="C343" s="2" t="n">
@@ -19930,10 +20313,10 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="3" t="n">
+      <c r="A344" s="5" t="n">
         <v>45242.875</v>
       </c>
-      <c r="B344" s="3" t="n">
+      <c r="B344" s="5" t="n">
         <v>45243.125</v>
       </c>
       <c r="C344" s="2" t="n">
@@ -19980,10 +20363,10 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="3" t="n">
+      <c r="A345" s="5" t="n">
         <v>45245.08333333334</v>
       </c>
-      <c r="B345" s="3" t="n">
+      <c r="B345" s="5" t="n">
         <v>45245.29166666666</v>
       </c>
       <c r="C345" s="2" t="n">
@@ -20030,10 +20413,10 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="3" t="n">
+      <c r="A346" s="5" t="n">
         <v>45251.41666666666</v>
       </c>
-      <c r="B346" s="3" t="n">
+      <c r="B346" s="5" t="n">
         <v>45251.58333333334</v>
       </c>
       <c r="C346" s="2" t="n">
@@ -20080,10 +20463,10 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="3" t="n">
+      <c r="A347" s="5" t="n">
         <v>45251.70833333334</v>
       </c>
-      <c r="B347" s="3" t="n">
+      <c r="B347" s="5" t="n">
         <v>45251.83333333334</v>
       </c>
       <c r="C347" s="2" t="n">
@@ -20130,10 +20513,10 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="3" t="n">
+      <c r="A348" s="5" t="n">
         <v>45253.83333333334</v>
       </c>
-      <c r="B348" s="3" t="n">
+      <c r="B348" s="5" t="n">
         <v>45255.625</v>
       </c>
       <c r="C348" s="2" t="n">
@@ -20180,10 +20563,10 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="3" t="n">
+      <c r="A349" s="5" t="n">
         <v>45255.75</v>
       </c>
-      <c r="B349" s="3" t="n">
+      <c r="B349" s="5" t="n">
         <v>45256.04166666666</v>
       </c>
       <c r="C349" s="2" t="n">
@@ -20230,10 +20613,10 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="3" t="n">
+      <c r="A350" s="5" t="n">
         <v>45256.16666666666</v>
       </c>
-      <c r="B350" s="3" t="n">
+      <c r="B350" s="5" t="n">
         <v>45257.04166666666</v>
       </c>
       <c r="C350" s="2" t="n">
@@ -20280,10 +20663,10 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="3" t="n">
+      <c r="A351" s="5" t="n">
         <v>45257.66666666666</v>
       </c>
-      <c r="B351" s="3" t="n">
+      <c r="B351" s="5" t="n">
         <v>45257.95833333334</v>
       </c>
       <c r="C351" s="2" t="n">
@@ -20330,10 +20713,10 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="3" t="n">
+      <c r="A352" s="5" t="n">
         <v>45259.29166666666</v>
       </c>
-      <c r="B352" s="3" t="n">
+      <c r="B352" s="5" t="n">
         <v>45259.83333333334</v>
       </c>
       <c r="C352" s="2" t="n">
@@ -20380,10 +20763,10 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="3" t="n">
+      <c r="A353" s="5" t="n">
         <v>45261</v>
       </c>
-      <c r="B353" s="3" t="n">
+      <c r="B353" s="5" t="n">
         <v>45261.20833333334</v>
       </c>
       <c r="C353" s="2" t="n">
@@ -20430,10 +20813,10 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="3" t="n">
+      <c r="A354" s="5" t="n">
         <v>45419.04166666666</v>
       </c>
-      <c r="B354" s="3" t="n">
+      <c r="B354" s="5" t="n">
         <v>45419.375</v>
       </c>
       <c r="C354" s="2" t="n">
@@ -20480,10 +20863,10 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="3" t="n">
+      <c r="A355" s="5" t="n">
         <v>45463.58333333334</v>
       </c>
-      <c r="B355" s="3" t="n">
+      <c r="B355" s="5" t="n">
         <v>45464</v>
       </c>
       <c r="C355" s="2" t="n">
@@ -20530,10 +20913,10 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="3" t="n">
+      <c r="A356" s="5" t="n">
         <v>45464.75</v>
       </c>
-      <c r="B356" s="3" t="n">
+      <c r="B356" s="5" t="n">
         <v>45464.875</v>
       </c>
       <c r="C356" s="2" t="n">
@@ -20580,10 +20963,10 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="3" t="n">
+      <c r="A357" s="5" t="n">
         <v>45466.45833333334</v>
       </c>
-      <c r="B357" s="3" t="n">
+      <c r="B357" s="5" t="n">
         <v>45466.58333333334</v>
       </c>
       <c r="C357" s="2" t="n">
@@ -20630,10 +21013,10 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="3" t="n">
+      <c r="A358" s="5" t="n">
         <v>45468.375</v>
       </c>
-      <c r="B358" s="3" t="n">
+      <c r="B358" s="5" t="n">
         <v>45468.54166666666</v>
       </c>
       <c r="C358" s="2" t="n">
@@ -20680,10 +21063,10 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="3" t="n">
+      <c r="A359" s="5" t="n">
         <v>45468.70833333334</v>
       </c>
-      <c r="B359" s="3" t="n">
+      <c r="B359" s="5" t="n">
         <v>45468.95833333334</v>
       </c>
       <c r="C359" s="2" t="n">
@@ -20730,10 +21113,10 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="3" t="n">
+      <c r="A360" s="5" t="n">
         <v>45469.75</v>
       </c>
-      <c r="B360" s="3" t="n">
+      <c r="B360" s="5" t="n">
         <v>45470.125</v>
       </c>
       <c r="C360" s="2" t="n">
@@ -20780,10 +21163,10 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="3" t="n">
+      <c r="A361" s="5" t="n">
         <v>45470.33333333334</v>
       </c>
-      <c r="B361" s="3" t="n">
+      <c r="B361" s="5" t="n">
         <v>45470.58333333334</v>
       </c>
       <c r="C361" s="2" t="n">
@@ -20830,10 +21213,10 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="3" t="n">
+      <c r="A362" s="5" t="n">
         <v>45470.95833333334</v>
       </c>
-      <c r="B362" s="3" t="n">
+      <c r="B362" s="5" t="n">
         <v>45471.125</v>
       </c>
       <c r="C362" s="2" t="n">
@@ -20880,10 +21263,10 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="3" t="n">
+      <c r="A363" s="5" t="n">
         <v>45475.29166666666</v>
       </c>
-      <c r="B363" s="3" t="n">
+      <c r="B363" s="5" t="n">
         <v>45475.45833333334</v>
       </c>
       <c r="C363" s="2" t="n">
@@ -20930,10 +21313,10 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="3" t="n">
+      <c r="A364" s="5" t="n">
         <v>45497.70833333334</v>
       </c>
-      <c r="B364" s="3" t="n">
+      <c r="B364" s="5" t="n">
         <v>45497.83333333334</v>
       </c>
       <c r="C364" s="2" t="n">
@@ -20980,10 +21363,10 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="3" t="n">
+      <c r="A365" s="5" t="n">
         <v>45505.33333333334</v>
       </c>
-      <c r="B365" s="3" t="n">
+      <c r="B365" s="5" t="n">
         <v>45505.58333333334</v>
       </c>
       <c r="C365" s="2" t="n">
@@ -21030,10 +21413,10 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="3" t="n">
+      <c r="A366" s="5" t="n">
         <v>45532.33333333334</v>
       </c>
-      <c r="B366" s="3" t="n">
+      <c r="B366" s="5" t="n">
         <v>45532.54166666666</v>
       </c>
       <c r="C366" s="2" t="n">
@@ -21080,10 +21463,10 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="3" t="n">
+      <c r="A367" s="5" t="n">
         <v>45536.45833333334</v>
       </c>
-      <c r="B367" s="3" t="n">
+      <c r="B367" s="5" t="n">
         <v>45536.58333333334</v>
       </c>
       <c r="C367" s="2" t="n">
@@ -21130,10 +21513,10 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="3" t="n">
+      <c r="A368" s="5" t="n">
         <v>45537.08333333334</v>
       </c>
-      <c r="B368" s="3" t="n">
+      <c r="B368" s="5" t="n">
         <v>45537.375</v>
       </c>
       <c r="C368" s="2" t="n">
@@ -21180,10 +21563,10 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="3" t="n">
+      <c r="A369" s="5" t="n">
         <v>45537.66666666666</v>
       </c>
-      <c r="B369" s="3" t="n">
+      <c r="B369" s="5" t="n">
         <v>45537.79166666666</v>
       </c>
       <c r="C369" s="2" t="n">
@@ -21230,10 +21613,10 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="3" t="n">
+      <c r="A370" s="5" t="n">
         <v>45565.95833333334</v>
       </c>
-      <c r="B370" s="3" t="n">
+      <c r="B370" s="5" t="n">
         <v>45566.08333333334</v>
       </c>
       <c r="C370" s="2" t="n">
@@ -21280,10 +21663,10 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="3" t="n">
+      <c r="A371" s="5" t="n">
         <v>45569.45833333334</v>
       </c>
-      <c r="B371" s="3" t="n">
+      <c r="B371" s="5" t="n">
         <v>45569.91666666666</v>
       </c>
       <c r="C371" s="2" t="n">
@@ -21330,10 +21713,10 @@
       </c>
     </row>
     <row r="372">
-      <c r="A372" s="3" t="n">
+      <c r="A372" s="5" t="n">
         <v>45573.625</v>
       </c>
-      <c r="B372" s="3" t="n">
+      <c r="B372" s="5" t="n">
         <v>45573.83333333334</v>
       </c>
       <c r="C372" s="2" t="n">
@@ -21380,10 +21763,10 @@
       </c>
     </row>
     <row r="373">
-      <c r="A373" s="3" t="n">
+      <c r="A373" s="5" t="n">
         <v>45580.54166666666</v>
       </c>
-      <c r="B373" s="3" t="n">
+      <c r="B373" s="5" t="n">
         <v>45580.91666666666</v>
       </c>
       <c r="C373" s="2" t="n">
@@ -21430,10 +21813,10 @@
       </c>
     </row>
     <row r="374">
-      <c r="A374" s="3" t="n">
+      <c r="A374" s="5" t="n">
         <v>45603.33333333334</v>
       </c>
-      <c r="B374" s="3" t="n">
+      <c r="B374" s="5" t="n">
         <v>45603.79166666666</v>
       </c>
       <c r="C374" s="2" t="n">
@@ -21480,10 +21863,10 @@
       </c>
     </row>
     <row r="375">
-      <c r="A375" s="3" t="n">
+      <c r="A375" s="5" t="n">
         <v>45624.66666666666</v>
       </c>
-      <c r="B375" s="3" t="n">
+      <c r="B375" s="5" t="n">
         <v>45624.95833333334</v>
       </c>
       <c r="C375" s="2" t="n">
@@ -21530,10 +21913,10 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376" s="3" t="n">
+      <c r="A376" s="5" t="n">
         <v>45625.16666666666</v>
       </c>
-      <c r="B376" s="3" t="n">
+      <c r="B376" s="5" t="n">
         <v>45625.83333333334</v>
       </c>
       <c r="C376" s="2" t="n">
@@ -21580,10 +21963,10 @@
       </c>
     </row>
     <row r="377">
-      <c r="A377" s="3" t="n">
+      <c r="A377" s="5" t="n">
         <v>45625.95833333334</v>
       </c>
-      <c r="B377" s="3" t="n">
+      <c r="B377" s="5" t="n">
         <v>45626.125</v>
       </c>
       <c r="C377" s="2" t="n">
@@ -21630,10 +22013,10 @@
       </c>
     </row>
     <row r="378">
-      <c r="A378" s="3" t="n">
+      <c r="A378" s="5" t="n">
         <v>45635.375</v>
       </c>
-      <c r="B378" s="3" t="n">
+      <c r="B378" s="5" t="n">
         <v>45635.58333333334</v>
       </c>
       <c r="C378" s="2" t="n">
@@ -21680,10 +22063,10 @@
       </c>
     </row>
     <row r="379">
-      <c r="A379" s="3" t="n">
+      <c r="A379" s="5" t="n">
         <v>45649.33333333334</v>
       </c>
-      <c r="B379" s="3" t="n">
+      <c r="B379" s="5" t="n">
         <v>45649.54166666666</v>
       </c>
       <c r="C379" s="2" t="n">
@@ -21730,10 +22113,10 @@
       </c>
     </row>
     <row r="380">
-      <c r="A380" s="3" t="n">
+      <c r="A380" s="5" t="n">
         <v>45663.29166666666</v>
       </c>
-      <c r="B380" s="3" t="n">
+      <c r="B380" s="5" t="n">
         <v>45663.79166666666</v>
       </c>
       <c r="C380" s="2" t="n">
@@ -21780,10 +22163,10 @@
       </c>
     </row>
     <row r="381">
-      <c r="A381" s="3" t="n">
+      <c r="A381" s="5" t="n">
         <v>45664.5</v>
       </c>
-      <c r="B381" s="3" t="n">
+      <c r="B381" s="5" t="n">
         <v>45664.66666666666</v>
       </c>
       <c r="C381" s="2" t="n">
@@ -21830,10 +22213,10 @@
       </c>
     </row>
     <row r="382">
-      <c r="A382" s="3" t="n">
+      <c r="A382" s="5" t="n">
         <v>45666.04166666666</v>
       </c>
-      <c r="B382" s="3" t="n">
+      <c r="B382" s="5" t="n">
         <v>45666.33333333334</v>
       </c>
       <c r="C382" s="2" t="n">
@@ -21880,10 +22263,10 @@
       </c>
     </row>
     <row r="383">
-      <c r="A383" s="3" t="n">
+      <c r="A383" s="5" t="n">
         <v>45667.45833333334</v>
       </c>
-      <c r="B383" s="3" t="n">
+      <c r="B383" s="5" t="n">
         <v>45673.41666666666</v>
       </c>
       <c r="C383" s="2" t="n">
@@ -21930,10 +22313,10 @@
       </c>
     </row>
     <row r="384">
-      <c r="A384" s="3" t="n">
+      <c r="A384" s="5" t="n">
         <v>45674.33333333334</v>
       </c>
-      <c r="B384" s="3" t="n">
+      <c r="B384" s="5" t="n">
         <v>45674.41666666666</v>
       </c>
       <c r="C384" s="2" t="n">
@@ -21980,10 +22363,10 @@
       </c>
     </row>
     <row r="385">
-      <c r="A385" s="3" t="n">
+      <c r="A385" s="5" t="n">
         <v>45704.79166666666</v>
       </c>
-      <c r="B385" s="3" t="n">
+      <c r="B385" s="5" t="n">
         <v>45705.29166666666</v>
       </c>
       <c r="C385" s="2" t="n">
@@ -22030,10 +22413,10 @@
       </c>
     </row>
     <row r="386">
-      <c r="A386" s="3" t="n">
+      <c r="A386" s="5" t="n">
         <v>45707.83333333334</v>
       </c>
-      <c r="B386" s="3" t="n">
+      <c r="B386" s="5" t="n">
         <v>45708.04166666666</v>
       </c>
       <c r="C386" s="2" t="n">
@@ -22080,10 +22463,10 @@
       </c>
     </row>
     <row r="387">
-      <c r="A387" s="3" t="n">
+      <c r="A387" s="5" t="n">
         <v>45723.41666666666</v>
       </c>
-      <c r="B387" s="3" t="n">
+      <c r="B387" s="5" t="n">
         <v>45723.75</v>
       </c>
       <c r="C387" s="2" t="n">
@@ -22130,10 +22513,10 @@
       </c>
     </row>
     <row r="388">
-      <c r="A388" s="3" t="n">
+      <c r="A388" s="5" t="n">
         <v>45727.70833333334</v>
       </c>
-      <c r="B388" s="3" t="n">
+      <c r="B388" s="5" t="n">
         <v>45727.79166666666</v>
       </c>
       <c r="C388" s="2" t="n">
@@ -22180,10 +22563,10 @@
       </c>
     </row>
     <row r="389">
-      <c r="A389" s="3" t="n">
+      <c r="A389" s="5" t="n">
         <v>45748.375</v>
       </c>
-      <c r="B389" s="3" t="n">
+      <c r="B389" s="5" t="n">
         <v>45748.70833333334</v>
       </c>
       <c r="C389" s="2" t="n">
@@ -22230,10 +22613,10 @@
       </c>
     </row>
     <row r="390">
-      <c r="A390" s="3" t="n">
+      <c r="A390" s="5" t="n">
         <v>45754.5</v>
       </c>
-      <c r="B390" s="3" t="n">
+      <c r="B390" s="5" t="n">
         <v>45754.875</v>
       </c>
       <c r="C390" s="2" t="n">
@@ -22280,10 +22663,10 @@
       </c>
     </row>
     <row r="391">
-      <c r="A391" s="3" t="n">
+      <c r="A391" s="5" t="n">
         <v>45778.33333333334</v>
       </c>
-      <c r="B391" s="3" t="n">
+      <c r="B391" s="5" t="n">
         <v>45778.45833333334</v>
       </c>
       <c r="C391" s="2" t="n">
@@ -22330,10 +22713,10 @@
       </c>
     </row>
     <row r="392">
-      <c r="A392" s="3" t="n">
+      <c r="A392" s="5" t="n">
         <v>45785.29166666666</v>
       </c>
-      <c r="B392" s="3" t="n">
+      <c r="B392" s="5" t="n">
         <v>45785.375</v>
       </c>
       <c r="C392" s="2" t="n">
@@ -22380,10 +22763,10 @@
       </c>
     </row>
     <row r="393">
-      <c r="A393" s="3" t="n">
+      <c r="A393" s="5" t="n">
         <v>45787.29166666666</v>
       </c>
-      <c r="B393" s="3" t="n">
+      <c r="B393" s="5" t="n">
         <v>45787.66666666666</v>
       </c>
       <c r="C393" s="2" t="n">
@@ -22430,10 +22813,10 @@
       </c>
     </row>
     <row r="394">
-      <c r="A394" s="3" t="n">
+      <c r="A394" s="5" t="n">
         <v>45791.33333333334</v>
       </c>
-      <c r="B394" s="3" t="n">
+      <c r="B394" s="5" t="n">
         <v>45791.83333333334</v>
       </c>
       <c r="C394" s="2" t="n">
@@ -22480,10 +22863,10 @@
       </c>
     </row>
     <row r="395">
-      <c r="A395" s="3" t="n">
+      <c r="A395" s="5" t="n">
         <v>45803.33333333334</v>
       </c>
-      <c r="B395" s="3" t="n">
+      <c r="B395" s="5" t="n">
         <v>45803.70833333334</v>
       </c>
       <c r="C395" s="2" t="n">
@@ -22530,10 +22913,10 @@
       </c>
     </row>
     <row r="396">
-      <c r="A396" s="3" t="n">
+      <c r="A396" s="5" t="n">
         <v>45806.375</v>
       </c>
-      <c r="B396" s="3" t="n">
+      <c r="B396" s="5" t="n">
         <v>45806.83333333334</v>
       </c>
       <c r="C396" s="2" t="n">
@@ -22580,10 +22963,10 @@
       </c>
     </row>
     <row r="397">
-      <c r="A397" s="3" t="n">
+      <c r="A397" s="5" t="n">
         <v>45808.45833333334</v>
       </c>
-      <c r="B397" s="3" t="n">
+      <c r="B397" s="5" t="n">
         <v>45808.75</v>
       </c>
       <c r="C397" s="2" t="n">
@@ -22630,10 +23013,10 @@
       </c>
     </row>
     <row r="398">
-      <c r="A398" s="3" t="n">
+      <c r="A398" s="5" t="n">
         <v>45810.29166666666</v>
       </c>
-      <c r="B398" s="3" t="n">
+      <c r="B398" s="5" t="n">
         <v>45810.75</v>
       </c>
       <c r="C398" s="2" t="n">
@@ -22680,10 +23063,10 @@
       </c>
     </row>
     <row r="399">
-      <c r="A399" s="3" t="n">
+      <c r="A399" s="5" t="n">
         <v>45810.875</v>
       </c>
-      <c r="B399" s="3" t="n">
+      <c r="B399" s="5" t="n">
         <v>45811.08333333334</v>
       </c>
       <c r="C399" s="2" t="n">
@@ -22730,10 +23113,10 @@
       </c>
     </row>
     <row r="400">
-      <c r="A400" s="3" t="n">
+      <c r="A400" s="5" t="n">
         <v>45811.41666666666</v>
       </c>
-      <c r="B400" s="3" t="n">
+      <c r="B400" s="5" t="n">
         <v>45811.58333333334</v>
       </c>
       <c r="C400" s="2" t="n">
@@ -22780,10 +23163,10 @@
       </c>
     </row>
     <row r="401">
-      <c r="A401" s="3" t="n">
+      <c r="A401" s="5" t="n">
         <v>45860.375</v>
       </c>
-      <c r="B401" s="3" t="n">
+      <c r="B401" s="5" t="n">
         <v>45860.66666666666</v>
       </c>
       <c r="C401" s="2" t="n">
@@ -22830,10 +23213,10 @@
       </c>
     </row>
     <row r="402">
-      <c r="A402" s="3" t="n">
+      <c r="A402" s="5" t="n">
         <v>45862.83333333334</v>
       </c>
-      <c r="B402" s="3" t="n">
+      <c r="B402" s="5" t="n">
         <v>45863</v>
       </c>
       <c r="C402" s="2" t="n">
@@ -22880,10 +23263,10 @@
       </c>
     </row>
     <row r="403">
-      <c r="A403" s="3" t="n">
+      <c r="A403" s="5" t="n">
         <v>45863.79166666666</v>
       </c>
-      <c r="B403" s="3" t="n">
+      <c r="B403" s="5" t="n">
         <v>45863.875</v>
       </c>
       <c r="C403" s="2" t="n">
@@ -22930,10 +23313,10 @@
       </c>
     </row>
     <row r="404">
-      <c r="A404" s="3" t="n">
+      <c r="A404" s="5" t="n">
         <v>45868.66666666666</v>
       </c>
-      <c r="B404" s="3" t="n">
+      <c r="B404" s="5" t="n">
         <v>45868.79166666666</v>
       </c>
       <c r="C404" s="2" t="n">
@@ -22980,10 +23363,10 @@
       </c>
     </row>
     <row r="405">
-      <c r="A405" s="3" t="n">
+      <c r="A405" s="5" t="n">
         <v>45869</v>
       </c>
-      <c r="B405" s="3" t="n">
+      <c r="B405" s="5" t="n">
         <v>45869.41666666666</v>
       </c>
       <c r="C405" s="2" t="n">
@@ -23030,10 +23413,10 @@
       </c>
     </row>
     <row r="406">
-      <c r="A406" s="3" t="n">
+      <c r="A406" s="5" t="n">
         <v>45869.79166666666</v>
       </c>
-      <c r="B406" s="3" t="n">
+      <c r="B406" s="5" t="n">
         <v>45869.875</v>
       </c>
       <c r="C406" s="2" t="n">
@@ -23080,10 +23463,10 @@
       </c>
     </row>
     <row r="407">
-      <c r="A407" s="3" t="n">
+      <c r="A407" s="5" t="n">
         <v>45870.375</v>
       </c>
-      <c r="B407" s="3" t="n">
+      <c r="B407" s="5" t="n">
         <v>45870.625</v>
       </c>
       <c r="C407" s="2" t="n">
@@ -23130,10 +23513,10 @@
       </c>
     </row>
     <row r="408">
-      <c r="A408" s="3" t="n">
+      <c r="A408" s="5" t="n">
         <v>45871.08333333334</v>
       </c>
-      <c r="B408" s="3" t="n">
+      <c r="B408" s="5" t="n">
         <v>45871.20833333334</v>
       </c>
       <c r="C408" s="2" t="n">
@@ -23180,10 +23563,10 @@
       </c>
     </row>
     <row r="409">
-      <c r="A409" s="3" t="n">
+      <c r="A409" s="5" t="n">
         <v>45901.45833333334</v>
       </c>
-      <c r="B409" s="3" t="n">
+      <c r="B409" s="5" t="n">
         <v>45901.58333333334</v>
       </c>
       <c r="C409" s="2" t="n">
@@ -23230,10 +23613,10 @@
       </c>
     </row>
     <row r="410">
-      <c r="A410" s="3" t="n">
+      <c r="A410" s="5" t="n">
         <v>45902.45833333334</v>
       </c>
-      <c r="B410" s="3" t="n">
+      <c r="B410" s="5" t="n">
         <v>45902.625</v>
       </c>
       <c r="C410" s="2" t="n">
@@ -23280,10 +23663,10 @@
       </c>
     </row>
     <row r="411">
-      <c r="A411" s="3" t="n">
+      <c r="A411" s="5" t="n">
         <v>45902.79166666666</v>
       </c>
-      <c r="B411" s="3" t="n">
+      <c r="B411" s="5" t="n">
         <v>45903.5</v>
       </c>
       <c r="C411" s="2" t="n">
@@ -23330,10 +23713,10 @@
       </c>
     </row>
     <row r="412">
-      <c r="A412" s="3" t="n">
+      <c r="A412" s="5" t="n">
         <v>45903.75</v>
       </c>
-      <c r="B412" s="3" t="n">
+      <c r="B412" s="5" t="n">
         <v>45904.08333333334</v>
       </c>
       <c r="C412" s="2" t="n">
@@ -23380,10 +23763,10 @@
       </c>
     </row>
     <row r="413">
-      <c r="A413" s="3" t="n">
+      <c r="A413" s="5" t="n">
         <v>45907.91666666666</v>
       </c>
-      <c r="B413" s="3" t="n">
+      <c r="B413" s="5" t="n">
         <v>45908.875</v>
       </c>
       <c r="C413" s="2" t="n">
@@ -23430,10 +23813,10 @@
       </c>
     </row>
     <row r="414">
-      <c r="A414" s="3" t="n">
+      <c r="A414" s="5" t="n">
         <v>45910.33333333334</v>
       </c>
-      <c r="B414" s="3" t="n">
+      <c r="B414" s="5" t="n">
         <v>45910.5</v>
       </c>
       <c r="C414" s="2" t="n">
@@ -23480,10 +23863,10 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" s="3" t="n">
+      <c r="A415" s="5" t="n">
         <v>45910.66666666666</v>
       </c>
-      <c r="B415" s="3" t="n">
+      <c r="B415" s="5" t="n">
         <v>45910.875</v>
       </c>
       <c r="C415" s="2" t="n">
@@ -23530,10 +23913,10 @@
       </c>
     </row>
     <row r="416">
-      <c r="A416" s="3" t="n">
+      <c r="A416" s="5" t="n">
         <v>45931.33333333334</v>
       </c>
-      <c r="B416" s="3" t="n">
+      <c r="B416" s="5" t="n">
         <v>45931.54166666666</v>
       </c>
       <c r="C416" s="2" t="n">
@@ -23580,10 +23963,10 @@
       </c>
     </row>
     <row r="417">
-      <c r="A417" s="3" t="n">
+      <c r="A417" s="5" t="n">
         <v>45938.29166666666</v>
       </c>
-      <c r="B417" s="3" t="n">
+      <c r="B417" s="5" t="n">
         <v>45938.875</v>
       </c>
       <c r="C417" s="2" t="n">
@@ -23630,10 +24013,10 @@
       </c>
     </row>
     <row r="418">
-      <c r="A418" s="3" t="n">
+      <c r="A418" s="5" t="n">
         <v>45944.375</v>
       </c>
-      <c r="B418" s="3" t="n">
+      <c r="B418" s="5" t="n">
         <v>45944.66666666666</v>
       </c>
       <c r="C418" s="2" t="n">
@@ -23680,10 +24063,10 @@
       </c>
     </row>
     <row r="419">
-      <c r="A419" s="3" t="n">
+      <c r="A419" s="5" t="n">
         <v>45944.83333333334</v>
       </c>
-      <c r="B419" s="3" t="n">
+      <c r="B419" s="5" t="n">
         <v>45945.25</v>
       </c>
       <c r="C419" s="2" t="n">
@@ -23730,10 +24113,10 @@
       </c>
     </row>
     <row r="420">
-      <c r="A420" s="3" t="n">
+      <c r="A420" s="5" t="n">
         <v>45958.41666666666</v>
       </c>
-      <c r="B420" s="3" t="n">
+      <c r="B420" s="5" t="n">
         <v>45959.04166666666</v>
       </c>
       <c r="C420" s="2" t="n">
@@ -23780,10 +24163,10 @@
       </c>
     </row>
     <row r="421">
-      <c r="A421" s="3" t="n">
+      <c r="A421" s="5" t="n">
         <v>45961.66666666666</v>
       </c>
-      <c r="B421" s="3" t="n">
+      <c r="B421" s="5" t="n">
         <v>45962.375</v>
       </c>
       <c r="C421" s="2" t="n">
@@ -23830,10 +24213,10 @@
       </c>
     </row>
     <row r="422">
-      <c r="A422" s="3" t="n">
+      <c r="A422" s="5" t="n">
         <v>45992.33333333334</v>
       </c>
-      <c r="B422" s="3" t="n">
+      <c r="B422" s="5" t="n">
         <v>45992.625</v>
       </c>
       <c r="C422" s="2" t="n">
@@ -23880,10 +24263,10 @@
       </c>
     </row>
     <row r="423">
-      <c r="A423" s="3" t="n">
+      <c r="A423" s="5" t="n">
         <v>45999.16666666666</v>
       </c>
-      <c r="B423" s="3" t="n">
+      <c r="B423" s="5" t="n">
         <v>45999.625</v>
       </c>
       <c r="C423" s="2" t="n">
@@ -23930,10 +24313,10 @@
       </c>
     </row>
     <row r="424">
-      <c r="A424" s="3" t="n">
+      <c r="A424" s="5" t="n">
         <v>46005</v>
       </c>
-      <c r="B424" s="3" t="n">
+      <c r="B424" s="5" t="n">
         <v>46005.16666666666</v>
       </c>
       <c r="C424" s="2" t="n">
@@ -23980,10 +24363,10 @@
       </c>
     </row>
     <row r="425">
-      <c r="A425" s="3" t="n">
+      <c r="A425" s="5" t="n">
         <v>46005.29166666666</v>
       </c>
-      <c r="B425" s="3" t="n">
+      <c r="B425" s="5" t="n">
         <v>46005.58333333334</v>
       </c>
       <c r="C425" s="2" t="n">
@@ -24030,10 +24413,10 @@
       </c>
     </row>
     <row r="426">
-      <c r="A426" s="3" t="n">
+      <c r="A426" s="5" t="n">
         <v>46011.29166666666</v>
       </c>
-      <c r="B426" s="3" t="n">
+      <c r="B426" s="5" t="n">
         <v>46011.5</v>
       </c>
       <c r="C426" s="2" t="n">
@@ -24080,10 +24463,10 @@
       </c>
     </row>
     <row r="427">
-      <c r="A427" s="3" t="n">
+      <c r="A427" s="5" t="n">
         <v>46067.70833333334</v>
       </c>
-      <c r="B427" s="3" t="n">
+      <c r="B427" s="5" t="n">
         <v>46068.29166666666</v>
       </c>
       <c r="C427" s="2" t="n">
@@ -24130,10 +24513,10 @@
       </c>
     </row>
     <row r="428">
-      <c r="A428" s="3" t="n">
+      <c r="A428" s="5" t="n">
         <v>46069.29166666666</v>
       </c>
-      <c r="B428" s="3" t="n">
+      <c r="B428" s="5" t="n">
         <v>46069.54166666666</v>
       </c>
       <c r="C428" s="2" t="n">
@@ -24180,10 +24563,10 @@
       </c>
     </row>
     <row r="429">
-      <c r="A429" s="3" t="n">
+      <c r="A429" s="5" t="n">
         <v>46070</v>
       </c>
-      <c r="B429" s="3" t="n">
+      <c r="B429" s="5" t="n">
         <v>46070.08333333334</v>
       </c>
       <c r="C429" s="2" t="n">
@@ -24230,10 +24613,10 @@
       </c>
     </row>
     <row r="430">
-      <c r="A430" s="3" t="n">
+      <c r="A430" s="5" t="n">
         <v>46078.33333333334</v>
       </c>
-      <c r="B430" s="3" t="n">
+      <c r="B430" s="5" t="n">
         <v>46078.41666666666</v>
       </c>
       <c r="C430" s="2" t="n">
@@ -24280,10 +24663,10 @@
       </c>
     </row>
     <row r="431">
-      <c r="A431" s="3" t="n">
+      <c r="A431" s="5" t="n">
         <v>46078.66666666666</v>
       </c>
-      <c r="B431" s="3" t="n">
+      <c r="B431" s="5" t="n">
         <v>46079.54166666666</v>
       </c>
       <c r="C431" s="2" t="n">
@@ -24330,10 +24713,10 @@
       </c>
     </row>
     <row r="432">
-      <c r="A432" s="3" t="n">
+      <c r="A432" s="5" t="n">
         <v>46131.33333333334</v>
       </c>
-      <c r="B432" s="3" t="n">
+      <c r="B432" s="5" t="n">
         <v>46131.5</v>
       </c>
       <c r="C432" s="2" t="n">
@@ -24380,10 +24763,10 @@
       </c>
     </row>
     <row r="433">
-      <c r="A433" s="3" t="n">
+      <c r="A433" s="5" t="n">
         <v>46137.45833333334</v>
       </c>
-      <c r="B433" s="3" t="n">
+      <c r="B433" s="5" t="n">
         <v>46137.58333333334</v>
       </c>
       <c r="C433" s="2" t="n">
@@ -26635,4 +27018,491 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>今回のテスト後戻し計画と、オンスペック中の増量実績の比較（FC1402 R-1401 EO FEED）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>ケース</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>負荷</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>変化量と所要時間</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>平均速度</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>1時間あたり</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>計画 テスト後戻し(切替前) 8/7</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>EOフィード 7.5 → 13.0 T/H</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>+5.5 T/H を 3 時間</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1.83 T/H per h</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1時間あたり +1.83 T/H</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>計画 テスト後戻し(LERA切替後) 8/6</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>EOフィード 7.5 → 13.0 T/H</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>+5.5 T/H を 4 時間</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1.37 T/H per h</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1時間あたり +1.37 T/H</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>実績 オンスペック中の増量 3 T/H超（26件）</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>中央値 +5.3 T/H</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>中央値 0.40 T/H per h</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>p90 0.66 / 最大 1.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>実績 段階的な増量の最速（2025/8/1）</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>11.60 → 17.70 T/H</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>+6.1 T/H を 5 時間</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1.02 T/H per h</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1時間の最大 +2.11 T/H</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>実績 最速（2022/5/7）</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>9.27 → 17.48 T/H</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>+8.2 T/H を 2 時間</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>4.11 T/H per h</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1時間の最大 +4.53 T/H</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>重ね書き用データ（増量開始を0時間、開始時からの増分 [T/H]）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>経過時間_h</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>計画 切替前 3h</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>計画 LERA切替後 4h</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>2020/3/9 実績</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>2020/7/27 実績</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="inlineStr">
+        <is>
+          <t>2021/1/6 実績</t>
+        </is>
+      </c>
+      <c r="G11" s="1" t="inlineStr">
+        <is>
+          <t>2022/5/7 実績</t>
+        </is>
+      </c>
+      <c r="H11" s="1" t="inlineStr">
+        <is>
+          <t>2020/8/30 実績</t>
+        </is>
+      </c>
+      <c r="I11" s="1" t="inlineStr">
+        <is>
+          <t>2021/1/28 実績</t>
+        </is>
+      </c>
+      <c r="J11" s="1" t="inlineStr">
+        <is>
+          <t>2025/8/1 実績</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>0</v>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>1.833111</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>1.374833</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>5.872868045171101</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>5.34204193300671</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>4.313159282472398</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>4.534269666406839</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>0.2242730469173839</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>0.2293326441446943</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>0.1412251790364589</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>3.666222</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>2.749667</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>8.098001670837402</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>7.580337928930918</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>7.472736621432833</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>8.212468834453157</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>1.026075648731656</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>0.4716406721538977</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>1.076659397549099</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>5.499333</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>4.1245</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>7.660055383046469</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>6.347868594328562</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>6.762435770034788</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>8.22403703053792</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>1.42031020561854</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>0.7808492570453218</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>1.908419222301907</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>4</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>5.499333</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>6.463310734430946</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>5.902754893567826</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>5.328041061825225</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>8.20181631935967</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>2.088183729648588</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>1.537176423072815</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>3.476501697434319</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>2.981324436929491</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>2.726120058165659</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>5.581894013086956</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>6</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>3.9298974442482</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>4.076862421565584</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>6.097244967354669</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>7</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>4.414647525946299</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>5.60543697728051</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>6.094171563254463</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>8</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>5.0955115003056</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>6.647012639045714</v>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>6.094942644966974</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>6.098801661862263</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>6.659689050780406</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>10</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>6.831952896383074</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>
--- a/outputs/FQY1530_FC1402_稼働調整速度.xlsx
+++ b/outputs/FQY1530_FC1402_稼働調整速度.xlsx
@@ -963,6 +963,412 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>増量開始からの FQY1530 増分 [T/H]</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'計画と実績_重ね書き'!B25</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'計画と実績_重ね書き'!$A$26:$A$44</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'計画と実績_重ね書き'!$B$26:$B$44</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'計画と実績_重ね書き'!C25</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'計画と実績_重ね書き'!$A$26:$A$44</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'計画と実績_重ね書き'!$C$26:$C$44</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'計画と実績_重ね書き'!D25</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'計画と実績_重ね書き'!$A$26:$A$44</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'計画と実績_重ね書き'!$D$26:$D$44</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'計画と実績_重ね書き'!E25</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'計画と実績_重ね書き'!$A$26:$A$44</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'計画と実績_重ね書き'!$E$26:$E$44</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'計画と実績_重ね書き'!F25</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'計画と実績_重ね書き'!$A$26:$A$44</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'計画と実績_重ね書き'!$F$26:$F$44</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <tx>
+            <strRef>
+              <f>'計画と実績_重ね書き'!G25</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'計画と実績_重ね書き'!$A$26:$A$44</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'計画と実績_重ね書き'!$G$26:$G$44</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="6"/>
+          <order val="6"/>
+          <tx>
+            <strRef>
+              <f>'計画と実績_重ね書き'!H25</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'計画と実績_重ね書き'!$A$26:$A$44</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'計画と実績_重ね書き'!$H$26:$H$44</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="7"/>
+          <order val="7"/>
+          <tx>
+            <strRef>
+              <f>'計画と実績_重ね書き'!I25</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'計画と実績_重ね書き'!$A$26:$A$44</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'計画と実績_重ね書き'!$I$26:$I$44</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="8"/>
+          <order val="8"/>
+          <tx>
+            <strRef>
+              <f>'計画と実績_重ね書き'!J25</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'計画と実績_重ね書き'!$A$26:$A$44</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'計画と実績_重ね書き'!$J$26:$J$44</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="9"/>
+          <order val="9"/>
+          <tx>
+            <strRef>
+              <f>'計画と実績_重ね書き'!K25</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'計画と実績_重ね書き'!$A$26:$A$44</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'計画と実績_重ね書き'!$K$26:$K$44</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>経過時間 [h]</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>FQY1530 の増分 [T/H]</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -1053,6 +1459,28 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>24</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -27026,7 +27454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -27501,6 +27929,507 @@
         <v>6.831952896383074</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>MEG（FQY1530 MEG TO TANKYARD）の増分 [T/H]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>経過時間_h</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>計画 切替前 3h</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="inlineStr">
+        <is>
+          <t>計画 LERA切替後 4h</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="inlineStr">
+        <is>
+          <t>2020/1/30 実績</t>
+        </is>
+      </c>
+      <c r="E25" s="1" t="inlineStr">
+        <is>
+          <t>2020/3/24 実績</t>
+        </is>
+      </c>
+      <c r="F25" s="1" t="inlineStr">
+        <is>
+          <t>2020/8/30 実績</t>
+        </is>
+      </c>
+      <c r="G25" s="1" t="inlineStr">
+        <is>
+          <t>2021/1/28 実績</t>
+        </is>
+      </c>
+      <c r="H25" s="1" t="inlineStr">
+        <is>
+          <t>2021/8/2 実績</t>
+        </is>
+      </c>
+      <c r="I25" s="1" t="inlineStr">
+        <is>
+          <t>2024/10/15 実績</t>
+        </is>
+      </c>
+      <c r="J25" s="1" t="inlineStr">
+        <is>
+          <t>2025/5/14 実績</t>
+        </is>
+      </c>
+      <c r="K25" s="1" t="inlineStr">
+        <is>
+          <t>2025/8/1 実績</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>0</v>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>2.736111</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>2.052083</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>0.1963649431864418</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>-0.05486475626627829</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>0.1306650702158585</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>-0.01123629252115776</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>-0.01943870226541833</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>1.035334385236105</v>
+      </c>
+      <c r="J27" s="4" t="n">
+        <v>0.4320560820897441</v>
+      </c>
+      <c r="K27" s="4" t="n">
+        <v>0.7812640619277964</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2</v>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>5.472222</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>4.104167</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>0.7667417526245117</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>0.2156480153401699</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>1.048104040357799</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>0.4878369172414168</v>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>0.01648787498474391</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>0.973355881373088</v>
+      </c>
+      <c r="J28" s="4" t="n">
+        <v>2.715850446224215</v>
+      </c>
+      <c r="K28" s="4" t="n">
+        <v>0.9240341297785442</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>8.208333</v>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>6.15625</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>1.902789497375487</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>0.6793937683105469</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>1.394475879139367</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>0.7330948193867997</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>1.267801742553711</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>1.363425656954448</v>
+      </c>
+      <c r="J29" s="4" t="n">
+        <v>4.18223803387748</v>
+      </c>
+      <c r="K29" s="4" t="n">
+        <v>3.246164248784382</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>4</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>8.208333</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>4.061471970876056</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>1.998685709635419</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>2.341144916746352</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>1.092616523106894</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>2.505589249928796</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>2.893385680516561</v>
+      </c>
+      <c r="J30" s="4" t="n">
+        <v>4.087619681623247</v>
+      </c>
+      <c r="K30" s="4" t="n">
+        <v>4.127854337692259</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>5</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>5.810054492950439</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>3.402608044942221</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>2.659334935082327</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>2.26016038576762</v>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>4.373897905349732</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>5.136948998769126</v>
+      </c>
+      <c r="J31" s="4" t="n">
+        <v>5.883036259280315</v>
+      </c>
+      <c r="K31" s="4" t="n">
+        <v>6.164156614939376</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>6</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>3.091094303131101</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>4.531453450520834</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>4.480190682941007</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>3.434533208211263</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>6.319001283645633</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>4.479518804550173</v>
+      </c>
+      <c r="J32" s="4" t="n">
+        <v>5.439953298833634</v>
+      </c>
+      <c r="K32" s="4" t="n">
+        <v>8.911237862904869</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>7</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>8.906867980957031</v>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>6.303603108723957</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>5.6379535431332</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>6.083834425608323</v>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>7.533382072448735</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>4.895454788208005</v>
+      </c>
+      <c r="J33" s="4" t="n">
+        <v>5.882527989016639</v>
+      </c>
+      <c r="K33" s="4" t="n">
+        <v>9.295704930623376</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>8</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>8.298733774820963</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>6.589895884195963</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>6.094332107967798</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>7.662670647303269</v>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>7.02731689453125</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>6.835093622207642</v>
+      </c>
+      <c r="J34" s="4" t="n">
+        <v>5.371490919060181</v>
+      </c>
+      <c r="K34" s="4" t="n">
+        <v>8.614725942611695</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>9</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>6.58566754659017</v>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>7.730531469980876</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>5.952882929907908</v>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>9.361223157246908</v>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>7.243621323903401</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>6.952600224812825</v>
+      </c>
+      <c r="J35" s="4" t="n">
+        <v>7.070447093910643</v>
+      </c>
+      <c r="K35" s="4" t="n">
+        <v>7.976365968916149</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>10</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>7.070047505696614</v>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>7.570717970530191</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>7.89683891561296</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>8.151904021898908</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>7.065001939137776</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>6.359993642171224</v>
+      </c>
+      <c r="J36" s="4" t="n">
+        <v>7.999753963417474</v>
+      </c>
+      <c r="K36" s="4" t="n">
+        <v>7.876377683877944</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>11</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>6.966552003224688</v>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>7.654768371582032</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>9.962636126412285</v>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>7.704159386952721</v>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>6.761663052241007</v>
+      </c>
+      <c r="J37" s="4" t="n">
+        <v>7.639652597904204</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>12</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>7.72112709681193</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>7.046022637685139</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>9.649530349307593</v>
+      </c>
+      <c r="J38" s="4" t="n">
+        <v>8.019119348790911</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>13</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>9.756594753265375</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>9.006109470261471</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>14</v>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>9.950515302022296</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>15</v>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>11.66039562225342</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>16</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>12.66244853337606</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>17</v>
+      </c>
+      <c r="D43" s="4" t="n">
+        <v>13.0039579073588</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>18</v>
+      </c>
+      <c r="D44" s="4" t="n">
+        <v>12.83010778427124</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/outputs/FQY1530_FC1402_稼働調整速度.xlsx
+++ b/outputs/FQY1530_FC1402_稼働調整速度.xlsx
@@ -866,38 +866,6 @@
             </numRef>
           </val>
         </ser>
-        <ser>
-          <idx val="8"/>
-          <order val="8"/>
-          <tx>
-            <strRef>
-              <f>'計画と実績_重ね書き'!J11</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'計画と実績_重ね書き'!$A$12:$A$22</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'計画と実績_重ね書き'!$J$12:$J$22</f>
-            </numRef>
-          </val>
-        </ser>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -1272,38 +1240,6 @@
             </numRef>
           </val>
         </ser>
-        <ser>
-          <idx val="9"/>
-          <order val="9"/>
-          <tx>
-            <strRef>
-              <f>'計画と実績_重ね書き'!K25</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'計画と実績_重ね書き'!$A$26:$A$44</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'計画と実績_重ね書き'!$K$26:$K$44</f>
-            </numRef>
-          </val>
-        </ser>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -1444,7 +1380,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>12</col>
+      <col>11</col>
       <colOff>0</colOff>
       <row>10</row>
       <rowOff>0</rowOff>
@@ -1466,7 +1402,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>13</col>
+      <col>12</col>
       <colOff>0</colOff>
       <row>24</row>
       <rowOff>0</rowOff>
@@ -27454,7 +27390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K44"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -27470,7 +27406,6 @@
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -27510,12 +27445,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>計画 テスト後戻し(切替前) 8/7</t>
+          <t>計画 テスト後戻し(切替前) 8/7  EOフィード</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EOフィード 7.5 → 13.0 T/H</t>
+          <t>7.5 → 13.0 T/H</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -27537,27 +27472,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>計画 テスト後戻し(LERA切替後) 8/6</t>
+          <t>計画 テスト後戻し(切替前) 8/7  MEG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EOフィード 7.5 → 13.0 T/H</t>
+          <t>7.6 → 15.8 T/H</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+5.5 T/H を 4 時間</t>
+          <t>+8.2 T/H を 3 時間</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.37 T/H per h</t>
+          <t>2.74 T/H per h</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1時間あたり +1.37 T/H</t>
+          <t>1時間あたり +2.74 T/H</t>
         </is>
       </c>
     </row>
@@ -27567,7 +27502,11 @@
           <t>実績 オンスペック中の増量 3 T/H超（26件）</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>EOフィード</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>中央値 +5.3 T/H</t>
@@ -27592,7 +27531,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11.60 → 17.70 T/H</t>
+          <t>EOフィード 11.60 → 17.70 T/H</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -27614,25 +27553,52 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>実績 段階的な増量の最速（2025/8/1）</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>MEG 12.71 → 21.86 T/H</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>+9.2 T/H を 6 時間</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1.52 T/H per h</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1時間の最大 +2.75 T/H</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>実績 最速（2022/5/7）</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>9.27 → 17.48 T/H</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>EOフィード 9.27 → 17.48 T/H</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>+8.2 T/H を 2 時間</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>4.11 T/H per h</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>1時間の最大 +4.53 T/H</t>
         </is>
@@ -27658,40 +27624,35 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>計画 LERA切替後 4h</t>
+          <t>2020/3/9 実績</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>2020/3/9 実績</t>
+          <t>2020/7/27 実績</t>
         </is>
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
-          <t>2020/7/27 実績</t>
+          <t>2021/1/6 実績</t>
         </is>
       </c>
       <c r="F11" s="1" t="inlineStr">
         <is>
-          <t>2021/1/6 実績</t>
+          <t>2022/5/7 実績</t>
         </is>
       </c>
       <c r="G11" s="1" t="inlineStr">
         <is>
-          <t>2022/5/7 実績</t>
+          <t>2020/8/30 実績</t>
         </is>
       </c>
       <c r="H11" s="1" t="inlineStr">
         <is>
-          <t>2020/8/30 実績</t>
+          <t>2021/1/28 実績</t>
         </is>
       </c>
       <c r="I11" s="1" t="inlineStr">
-        <is>
-          <t>2021/1/28 実績</t>
-        </is>
-      </c>
-      <c r="J11" s="1" t="inlineStr">
         <is>
           <t>2025/8/1 実績</t>
         </is>
@@ -27723,9 +27684,6 @@
         <v>0</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -27737,27 +27695,24 @@
         <v>1.833111</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1.374833</v>
+        <v>5.872868045171101</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>5.872868045171101</v>
+        <v>5.34204193300671</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>5.34204193300671</v>
+        <v>4.313159282472398</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>4.313159282472398</v>
+        <v>4.534269666406839</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>4.534269666406839</v>
+        <v>0.2242730469173839</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.2242730469173839</v>
+        <v>0.2293326441446943</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.2293326441446943</v>
-      </c>
-      <c r="J13" s="4" t="n">
         <v>0.1412251790364589</v>
       </c>
     </row>
@@ -27769,27 +27724,24 @@
         <v>3.666222</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2.749667</v>
+        <v>8.098001670837402</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>8.098001670837402</v>
+        <v>7.580337928930918</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>7.580337928930918</v>
+        <v>7.472736621432833</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>7.472736621432833</v>
+        <v>8.212468834453157</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>8.212468834453157</v>
+        <v>1.026075648731656</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.026075648731656</v>
+        <v>0.4716406721538977</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.4716406721538977</v>
-      </c>
-      <c r="J14" s="4" t="n">
         <v>1.076659397549099</v>
       </c>
     </row>
@@ -27801,27 +27753,24 @@
         <v>5.499333</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>4.1245</v>
+        <v>7.660055383046469</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>7.660055383046469</v>
+        <v>6.347868594328562</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>6.347868594328562</v>
+        <v>6.762435770034788</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>6.762435770034788</v>
+        <v>8.22403703053792</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>8.22403703053792</v>
+        <v>1.42031020561854</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.42031020561854</v>
+        <v>0.7808492570453218</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.7808492570453218</v>
-      </c>
-      <c r="J15" s="4" t="n">
         <v>1.908419222301907</v>
       </c>
     </row>
@@ -27830,27 +27779,24 @@
         <v>4</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>5.499333</v>
+        <v>6.463310734430946</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>6.463310734430946</v>
+        <v>5.902754893567826</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>5.902754893567826</v>
+        <v>5.328041061825225</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>5.328041061825225</v>
+        <v>8.20181631935967</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>8.20181631935967</v>
+        <v>2.088183729648588</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2.088183729648588</v>
+        <v>1.537176423072815</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.537176423072815</v>
-      </c>
-      <c r="J16" s="4" t="n">
         <v>3.476501697434319</v>
       </c>
     </row>
@@ -27858,13 +27804,13 @@
       <c r="A17" t="n">
         <v>5</v>
       </c>
+      <c r="G17" s="4" t="n">
+        <v>2.981324436929491</v>
+      </c>
       <c r="H17" s="4" t="n">
-        <v>2.981324436929491</v>
+        <v>2.726120058165659</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.726120058165659</v>
-      </c>
-      <c r="J17" s="4" t="n">
         <v>5.581894013086956</v>
       </c>
     </row>
@@ -27872,13 +27818,13 @@
       <c r="A18" t="n">
         <v>6</v>
       </c>
+      <c r="G18" s="4" t="n">
+        <v>3.9298974442482</v>
+      </c>
       <c r="H18" s="4" t="n">
-        <v>3.9298974442482</v>
+        <v>4.076862421565584</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>4.076862421565584</v>
-      </c>
-      <c r="J18" s="4" t="n">
         <v>6.097244967354669</v>
       </c>
     </row>
@@ -27886,13 +27832,13 @@
       <c r="A19" t="n">
         <v>7</v>
       </c>
+      <c r="G19" s="4" t="n">
+        <v>4.414647525946299</v>
+      </c>
       <c r="H19" s="4" t="n">
-        <v>4.414647525946299</v>
+        <v>5.60543697728051</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>5.60543697728051</v>
-      </c>
-      <c r="J19" s="4" t="n">
         <v>6.094171563254463</v>
       </c>
     </row>
@@ -27900,13 +27846,13 @@
       <c r="A20" t="n">
         <v>8</v>
       </c>
+      <c r="G20" s="4" t="n">
+        <v>5.0955115003056</v>
+      </c>
       <c r="H20" s="4" t="n">
-        <v>5.0955115003056</v>
+        <v>6.647012639045714</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>6.647012639045714</v>
-      </c>
-      <c r="J20" s="4" t="n">
         <v>6.094942644966974</v>
       </c>
     </row>
@@ -27914,10 +27860,10 @@
       <c r="A21" t="n">
         <v>9</v>
       </c>
+      <c r="G21" s="4" t="n">
+        <v>6.098801661862263</v>
+      </c>
       <c r="H21" s="4" t="n">
-        <v>6.098801661862263</v>
-      </c>
-      <c r="I21" s="4" t="n">
         <v>6.659689050780406</v>
       </c>
     </row>
@@ -27925,7 +27871,7 @@
       <c r="A22" t="n">
         <v>10</v>
       </c>
-      <c r="H22" s="4" t="n">
+      <c r="G22" s="4" t="n">
         <v>6.831952896383074</v>
       </c>
     </row>
@@ -27949,45 +27895,40 @@
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>計画 LERA切替後 4h</t>
+          <t>2020/1/30 実績</t>
         </is>
       </c>
       <c r="D25" s="1" t="inlineStr">
         <is>
-          <t>2020/1/30 実績</t>
+          <t>2020/3/24 実績</t>
         </is>
       </c>
       <c r="E25" s="1" t="inlineStr">
         <is>
-          <t>2020/3/24 実績</t>
+          <t>2020/8/30 実績</t>
         </is>
       </c>
       <c r="F25" s="1" t="inlineStr">
         <is>
-          <t>2020/8/30 実績</t>
+          <t>2021/1/28 実績</t>
         </is>
       </c>
       <c r="G25" s="1" t="inlineStr">
         <is>
-          <t>2021/1/28 実績</t>
+          <t>2021/8/2 実績</t>
         </is>
       </c>
       <c r="H25" s="1" t="inlineStr">
         <is>
-          <t>2021/8/2 実績</t>
+          <t>2024/10/15 実績</t>
         </is>
       </c>
       <c r="I25" s="1" t="inlineStr">
         <is>
-          <t>2024/10/15 実績</t>
+          <t>2025/5/14 実績</t>
         </is>
       </c>
       <c r="J25" s="1" t="inlineStr">
-        <is>
-          <t>2025/5/14 実績</t>
-        </is>
-      </c>
-      <c r="K25" s="1" t="inlineStr">
         <is>
           <t>2025/8/1 実績</t>
         </is>
@@ -28022,9 +27963,6 @@
         <v>0</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -28036,30 +27974,27 @@
         <v>2.736111</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2.052083</v>
+        <v>0.1963649431864418</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.1963649431864418</v>
+        <v>-0.05486475626627829</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.05486475626627829</v>
+        <v>0.1306650702158585</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.1306650702158585</v>
+        <v>-0.01123629252115776</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.01123629252115776</v>
+        <v>-0.01943870226541833</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.01943870226541833</v>
+        <v>1.035334385236105</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>1.035334385236105</v>
+        <v>0.4320560820897441</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.4320560820897441</v>
-      </c>
-      <c r="K27" s="4" t="n">
         <v>0.7812640619277964</v>
       </c>
     </row>
@@ -28071,30 +28006,27 @@
         <v>5.472222</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>4.104167</v>
+        <v>0.7667417526245117</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.7667417526245117</v>
+        <v>0.2156480153401699</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.2156480153401699</v>
+        <v>1.048104040357799</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1.048104040357799</v>
+        <v>0.4878369172414168</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.4878369172414168</v>
+        <v>0.01648787498474391</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.01648787498474391</v>
+        <v>0.973355881373088</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.973355881373088</v>
+        <v>2.715850446224215</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>2.715850446224215</v>
-      </c>
-      <c r="K28" s="4" t="n">
         <v>0.9240341297785442</v>
       </c>
     </row>
@@ -28106,30 +28038,27 @@
         <v>8.208333</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>6.15625</v>
+        <v>1.902789497375487</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>1.902789497375487</v>
+        <v>0.6793937683105469</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.6793937683105469</v>
+        <v>1.394475879139367</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1.394475879139367</v>
+        <v>0.7330948193867997</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.7330948193867997</v>
+        <v>1.267801742553711</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.267801742553711</v>
+        <v>1.363425656954448</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>1.363425656954448</v>
+        <v>4.18223803387748</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>4.18223803387748</v>
-      </c>
-      <c r="K29" s="4" t="n">
         <v>3.246164248784382</v>
       </c>
     </row>
@@ -28138,30 +28067,27 @@
         <v>4</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>8.208333</v>
+        <v>4.061471970876056</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>4.061471970876056</v>
+        <v>1.998685709635419</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.998685709635419</v>
+        <v>2.341144916746352</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2.341144916746352</v>
+        <v>1.092616523106894</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>1.092616523106894</v>
+        <v>2.505589249928796</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>2.505589249928796</v>
+        <v>2.893385680516561</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>2.893385680516561</v>
+        <v>4.087619681623247</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>4.087619681623247</v>
-      </c>
-      <c r="K30" s="4" t="n">
         <v>4.127854337692259</v>
       </c>
     </row>
@@ -28169,28 +28095,28 @@
       <c r="A31" t="n">
         <v>5</v>
       </c>
+      <c r="C31" s="4" t="n">
+        <v>5.810054492950439</v>
+      </c>
       <c r="D31" s="4" t="n">
-        <v>5.810054492950439</v>
+        <v>3.402608044942221</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>3.402608044942221</v>
+        <v>2.659334935082327</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>2.659334935082327</v>
+        <v>2.26016038576762</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>2.26016038576762</v>
+        <v>4.373897905349732</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>4.373897905349732</v>
+        <v>5.136948998769126</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>5.136948998769126</v>
+        <v>5.883036259280315</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>5.883036259280315</v>
-      </c>
-      <c r="K31" s="4" t="n">
         <v>6.164156614939376</v>
       </c>
     </row>
@@ -28198,28 +28124,28 @@
       <c r="A32" t="n">
         <v>6</v>
       </c>
+      <c r="C32" s="4" t="n">
+        <v>3.091094303131101</v>
+      </c>
       <c r="D32" s="4" t="n">
-        <v>3.091094303131101</v>
+        <v>4.531453450520834</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>4.531453450520834</v>
+        <v>4.480190682941007</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4.480190682941007</v>
+        <v>3.434533208211263</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>3.434533208211263</v>
+        <v>6.319001283645633</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>6.319001283645633</v>
+        <v>4.479518804550173</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>4.479518804550173</v>
+        <v>5.439953298833634</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>5.439953298833634</v>
-      </c>
-      <c r="K32" s="4" t="n">
         <v>8.911237862904869</v>
       </c>
     </row>
@@ -28227,28 +28153,28 @@
       <c r="A33" t="n">
         <v>7</v>
       </c>
+      <c r="C33" s="4" t="n">
+        <v>8.906867980957031</v>
+      </c>
       <c r="D33" s="4" t="n">
-        <v>8.906867980957031</v>
+        <v>6.303603108723957</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>6.303603108723957</v>
+        <v>5.6379535431332</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>5.6379535431332</v>
+        <v>6.083834425608323</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>6.083834425608323</v>
+        <v>7.533382072448735</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>7.533382072448735</v>
+        <v>4.895454788208005</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>4.895454788208005</v>
+        <v>5.882527989016639</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>5.882527989016639</v>
-      </c>
-      <c r="K33" s="4" t="n">
         <v>9.295704930623376</v>
       </c>
     </row>
@@ -28256,28 +28182,28 @@
       <c r="A34" t="n">
         <v>8</v>
       </c>
+      <c r="C34" s="4" t="n">
+        <v>8.298733774820963</v>
+      </c>
       <c r="D34" s="4" t="n">
-        <v>8.298733774820963</v>
+        <v>6.589895884195963</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>6.589895884195963</v>
+        <v>6.094332107967798</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>6.094332107967798</v>
+        <v>7.662670647303269</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>7.662670647303269</v>
+        <v>7.02731689453125</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>7.02731689453125</v>
+        <v>6.835093622207642</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>6.835093622207642</v>
+        <v>5.371490919060181</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>5.371490919060181</v>
-      </c>
-      <c r="K34" s="4" t="n">
         <v>8.614725942611695</v>
       </c>
     </row>
@@ -28285,28 +28211,28 @@
       <c r="A35" t="n">
         <v>9</v>
       </c>
+      <c r="C35" s="4" t="n">
+        <v>6.58566754659017</v>
+      </c>
       <c r="D35" s="4" t="n">
-        <v>6.58566754659017</v>
+        <v>7.730531469980876</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>7.730531469980876</v>
+        <v>5.952882929907908</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>5.952882929907908</v>
+        <v>9.361223157246908</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>9.361223157246908</v>
+        <v>7.243621323903401</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>7.243621323903401</v>
+        <v>6.952600224812825</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>6.952600224812825</v>
+        <v>7.070447093910643</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>7.070447093910643</v>
-      </c>
-      <c r="K35" s="4" t="n">
         <v>7.976365968916149</v>
       </c>
     </row>
@@ -28314,28 +28240,28 @@
       <c r="A36" t="n">
         <v>10</v>
       </c>
+      <c r="C36" s="4" t="n">
+        <v>7.070047505696614</v>
+      </c>
       <c r="D36" s="4" t="n">
-        <v>7.070047505696614</v>
+        <v>7.570717970530191</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>7.570717970530191</v>
+        <v>7.89683891561296</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>7.89683891561296</v>
+        <v>8.151904021898908</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>8.151904021898908</v>
+        <v>7.065001939137776</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>7.065001939137776</v>
+        <v>6.359993642171224</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>6.359993642171224</v>
+        <v>7.999753963417474</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>7.999753963417474</v>
-      </c>
-      <c r="K36" s="4" t="n">
         <v>7.876377683877944</v>
       </c>
     </row>
@@ -28343,22 +28269,22 @@
       <c r="A37" t="n">
         <v>11</v>
       </c>
+      <c r="C37" s="4" t="n">
+        <v>6.966552003224688</v>
+      </c>
       <c r="D37" s="4" t="n">
-        <v>6.966552003224688</v>
+        <v>7.654768371582032</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>7.654768371582032</v>
+        <v>9.962636126412285</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>9.962636126412285</v>
-      </c>
-      <c r="G37" s="4" t="n">
         <v>7.704159386952721</v>
       </c>
+      <c r="H37" s="4" t="n">
+        <v>6.761663052241007</v>
+      </c>
       <c r="I37" s="4" t="n">
-        <v>6.761663052241007</v>
-      </c>
-      <c r="J37" s="4" t="n">
         <v>7.639652597904204</v>
       </c>
     </row>
@@ -28366,16 +28292,16 @@
       <c r="A38" t="n">
         <v>12</v>
       </c>
+      <c r="C38" s="4" t="n">
+        <v>7.72112709681193</v>
+      </c>
       <c r="D38" s="4" t="n">
-        <v>7.72112709681193</v>
+        <v>7.046022637685139</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>7.046022637685139</v>
-      </c>
-      <c r="F38" s="4" t="n">
         <v>9.649530349307593</v>
       </c>
-      <c r="J38" s="4" t="n">
+      <c r="I38" s="4" t="n">
         <v>8.019119348790911</v>
       </c>
     </row>
@@ -28383,10 +28309,10 @@
       <c r="A39" t="n">
         <v>13</v>
       </c>
-      <c r="D39" s="4" t="n">
+      <c r="C39" s="4" t="n">
         <v>9.756594753265375</v>
       </c>
-      <c r="F39" s="4" t="n">
+      <c r="E39" s="4" t="n">
         <v>9.006109470261471</v>
       </c>
     </row>
@@ -28394,7 +28320,7 @@
       <c r="A40" t="n">
         <v>14</v>
       </c>
-      <c r="D40" s="4" t="n">
+      <c r="C40" s="4" t="n">
         <v>9.950515302022296</v>
       </c>
     </row>
@@ -28402,7 +28328,7 @@
       <c r="A41" t="n">
         <v>15</v>
       </c>
-      <c r="D41" s="4" t="n">
+      <c r="C41" s="4" t="n">
         <v>11.66039562225342</v>
       </c>
     </row>
@@ -28410,7 +28336,7 @@
       <c r="A42" t="n">
         <v>16</v>
       </c>
-      <c r="D42" s="4" t="n">
+      <c r="C42" s="4" t="n">
         <v>12.66244853337606</v>
       </c>
     </row>
@@ -28418,7 +28344,7 @@
       <c r="A43" t="n">
         <v>17</v>
       </c>
-      <c r="D43" s="4" t="n">
+      <c r="C43" s="4" t="n">
         <v>13.0039579073588</v>
       </c>
     </row>
@@ -28426,7 +28352,7 @@
       <c r="A44" t="n">
         <v>18</v>
       </c>
-      <c r="D44" s="4" t="n">
+      <c r="C44" s="4" t="n">
         <v>12.83010778427124</v>
       </c>
     </row>
